--- a/inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
+++ b/inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\src\thermal_deformation\data_femap_deformation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_femap_deformation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01ACDC0E-3F29-4BAC-85D0-337C02EA9711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E22735D-1005-4E31-A785-05B72A4F7057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{835C13A9-C35C-41B8-BC0E-5CC3981CD98B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{2569F954-8B1F-45EB-813A-98718E5BC2EA}"/>
   </bookViews>
   <sheets>
     <sheet name="ノード" sheetId="1" r:id="rId1"/>
@@ -262,29 +262,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BA6F4A0F-7517-42BB-AAB4-44ED1CAD0964}" name="テーブル1" displayName="テーブル1" ref="A1:T33" totalsRowShown="0">
-  <autoFilter ref="A1:T33" xr:uid="{BA6F4A0F-7517-42BB-AAB4-44ED1CAD0964}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A85C5E47-55B6-4F59-A7AD-77E0572DC1BE}" name="テーブル1" displayName="テーブル1" ref="A1:T33" totalsRowShown="0">
+  <autoFilter ref="A1:T33" xr:uid="{A85C5E47-55B6-4F59-A7AD-77E0572DC1BE}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{B25DD29C-7284-4D9E-889B-64F7A6BCC944}" name="セット ID"/>
-    <tableColumn id="2" xr3:uid="{3FC1620C-97FC-4D2A-9E6C-73EB7B389B16}" name="セットの値"/>
-    <tableColumn id="3" xr3:uid="{DCFB4E71-246A-4259-AF6F-7FA135418898}" name="セット　タイトル"/>
-    <tableColumn id="4" xr3:uid="{9073D929-C954-45C4-8369-2ECA447EFA75}" name="スタディID"/>
-    <tableColumn id="5" xr3:uid="{4F9F1184-A46D-4B00-A8F7-E9479686B3BF}" name="ノード 15858, 1..Total Translation"/>
-    <tableColumn id="6" xr3:uid="{67972A7C-2313-4A9E-8BCB-0999FCD941F6}" name="ノード 19459, 1..Total Translation"/>
-    <tableColumn id="7" xr3:uid="{DC89A0B2-E65A-4BCD-9A29-DCF4383F3F12}" name="ノード 15858, 2..T1 Translation"/>
-    <tableColumn id="8" xr3:uid="{FAE0ECCC-4E34-4B3F-9E80-12E5053FDCA6}" name="ノード 19459, 2..T1 Translation"/>
-    <tableColumn id="9" xr3:uid="{B6133833-8CC8-496B-B757-7930E7E0D2E7}" name="ノード 15858, 3..T2 Translation"/>
-    <tableColumn id="10" xr3:uid="{D1B60984-880E-44E9-AA14-AEDB73A563DD}" name="ノード 19459, 3..T2 Translation"/>
-    <tableColumn id="11" xr3:uid="{5E86945B-89DA-463D-978F-DF3FA24A4141}" name="ノード 15858, 4..T3 Translation"/>
-    <tableColumn id="12" xr3:uid="{27299B7C-1D1C-481D-80D0-D577E1224151}" name="ノード 19459, 4..T3 Translation"/>
-    <tableColumn id="13" xr3:uid="{F8B9D4AC-D413-47C0-AEEC-61A80861EB91}" name="ノード 15858, 5..Total Rotation"/>
-    <tableColumn id="14" xr3:uid="{97AE0B84-C904-4A13-B461-32390D67206F}" name="ノード 19459, 5..Total Rotation"/>
-    <tableColumn id="15" xr3:uid="{D8F3BF48-C032-40C6-9E76-6A145E621453}" name="ノード 15858, 6..R1 Rotation"/>
-    <tableColumn id="16" xr3:uid="{97B19E74-379D-42BD-A29C-78AF174F0067}" name="ノード 19459, 6..R1 Rotation"/>
-    <tableColumn id="17" xr3:uid="{6E6EF841-71F6-43EA-AF21-C4097BC27F78}" name="ノード 15858, 7..R2 Rotation"/>
-    <tableColumn id="18" xr3:uid="{831985A5-478C-4C9E-9C5C-E07D44F31DA9}" name="ノード 19459, 7..R2 Rotation"/>
-    <tableColumn id="19" xr3:uid="{D4BB7D09-5AE0-4407-998C-61E727A02027}" name="ノード 15858, 8..R3 Rotation"/>
-    <tableColumn id="20" xr3:uid="{CD1800A2-3511-42D5-B439-FB9CC2AFA7BE}" name="ノード 19459, 8..R3 Rotation"/>
+    <tableColumn id="1" xr3:uid="{6F478318-A588-4EE6-A08A-AF1A3469BFA3}" name="セット ID"/>
+    <tableColumn id="2" xr3:uid="{8307019A-C967-4B4C-B121-A4B120B29EC2}" name="セットの値"/>
+    <tableColumn id="3" xr3:uid="{FC337198-54DC-4FAB-A088-699495B393DD}" name="セット　タイトル"/>
+    <tableColumn id="4" xr3:uid="{8D5298C8-E7AB-4C29-9AA0-3DF78EF148C8}" name="スタディID"/>
+    <tableColumn id="5" xr3:uid="{649B9ED2-8683-46E3-92C8-6755F3795A6B}" name="ノード 15858, 1..Total Translation"/>
+    <tableColumn id="6" xr3:uid="{09870565-0501-4FCB-A057-7A155CD3F07A}" name="ノード 19459, 1..Total Translation"/>
+    <tableColumn id="7" xr3:uid="{F9D3E402-876C-431A-BCC1-43F339230841}" name="ノード 15858, 2..T1 Translation"/>
+    <tableColumn id="8" xr3:uid="{F25B9A4F-E3D9-4F06-810E-A0BF513CD583}" name="ノード 19459, 2..T1 Translation"/>
+    <tableColumn id="9" xr3:uid="{84C9DF86-B2B2-4816-B30B-6D4C9FFED42E}" name="ノード 15858, 3..T2 Translation"/>
+    <tableColumn id="10" xr3:uid="{11F6C372-69E4-4F61-A544-4D38C919673E}" name="ノード 19459, 3..T2 Translation"/>
+    <tableColumn id="11" xr3:uid="{213D8AD8-0092-4A98-9EF4-876EBD7AEE5A}" name="ノード 15858, 4..T3 Translation"/>
+    <tableColumn id="12" xr3:uid="{AB5AF530-B282-47C4-8B30-A7B98DD48A98}" name="ノード 19459, 4..T3 Translation"/>
+    <tableColumn id="13" xr3:uid="{F948FB8A-FBB2-4F3A-B3BC-0D2BEBDF6CB2}" name="ノード 15858, 5..Total Rotation"/>
+    <tableColumn id="14" xr3:uid="{2020A580-CB26-4285-98B1-F1224F432EF4}" name="ノード 19459, 5..Total Rotation"/>
+    <tableColumn id="15" xr3:uid="{F966FF6C-23C8-485C-961D-419DC8F7B3BC}" name="ノード 15858, 6..R1 Rotation"/>
+    <tableColumn id="16" xr3:uid="{09CE6672-8367-48BC-866D-4C51CBD8A3CD}" name="ノード 19459, 6..R1 Rotation"/>
+    <tableColumn id="17" xr3:uid="{594440B4-5F18-45FA-8538-F745068DF8FA}" name="ノード 15858, 7..R2 Rotation"/>
+    <tableColumn id="18" xr3:uid="{F27BFAD1-681A-4F80-9430-E374592B6A1E}" name="ノード 19459, 7..R2 Rotation"/>
+    <tableColumn id="19" xr3:uid="{A4DDA5AD-4459-4E32-98DB-D7601AE59420}" name="ノード 15858, 8..R3 Rotation"/>
+    <tableColumn id="20" xr3:uid="{CC95190D-E0E3-496B-A612-F68606C93AB2}" name="ノード 19459, 8..R3 Rotation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -606,7 +606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9BCFF47-281E-4035-B9E3-DA5B6A024CD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7CAE6A-4F4C-4314-965A-45A72B02E914}">
   <dimension ref="A1:T33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -696,52 +696,52 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1.8049194477498531E-3</v>
+        <v>3.0625221552327275E-4</v>
       </c>
       <c r="F2">
-        <v>1.1950430780416355E-4</v>
+        <v>2.2888018065714277E-5</v>
       </c>
       <c r="G2">
-        <v>7.5850810389965773E-5</v>
+        <v>2.7367854272597469E-5</v>
       </c>
       <c r="H2">
-        <v>8.7502266978845E-5</v>
+        <v>-1.4404878129425924E-5</v>
       </c>
       <c r="I2">
-        <v>1.8671936413738877E-4</v>
+        <v>-2.683658676687628E-4</v>
       </c>
       <c r="J2">
-        <v>8.1391604908276349E-5</v>
+        <v>-1.7774384104995988E-5</v>
       </c>
       <c r="K2">
-        <v>-1.7936322838068008E-3</v>
+        <v>1.4498685777653009E-4</v>
       </c>
       <c r="L2">
-        <v>-1.9981402488156164E-7</v>
+        <v>6.5735531507016276E-7</v>
       </c>
       <c r="M2">
-        <v>1.4210649533197284E-4</v>
+        <v>6.1502563767135143E-4</v>
       </c>
       <c r="N2">
-        <v>2.3336357116932049E-5</v>
+        <v>4.5239878090796992E-5</v>
       </c>
       <c r="O2">
-        <v>1.415950246155262E-4</v>
+        <v>-6.1213696608319879E-4</v>
       </c>
       <c r="P2">
-        <v>1.6131371012306772E-5</v>
+        <v>-2.1351768737076782E-5</v>
       </c>
       <c r="Q2">
-        <v>-6.3303386923507787E-6</v>
+        <v>-5.4868098231963813E-5</v>
       </c>
       <c r="R2">
-        <v>1.3281253814056981E-5</v>
+        <v>-3.0606010113842785E-5</v>
       </c>
       <c r="S2">
-        <v>1.0248411854263395E-5</v>
+        <v>-2.3115391741157509E-5</v>
       </c>
       <c r="T2">
-        <v>1.0390991519670933E-5</v>
+        <v>-2.5573828679625876E-5</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.4">
@@ -758,52 +758,52 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1.8049194477498531E-3</v>
+        <v>3.0625221552327275E-4</v>
       </c>
       <c r="F3">
-        <v>1.1950430780416355E-4</v>
+        <v>2.2888018065714277E-5</v>
       </c>
       <c r="G3">
-        <v>7.5850810389965773E-5</v>
+        <v>2.7367854272597469E-5</v>
       </c>
       <c r="H3">
-        <v>8.7502266978845E-5</v>
+        <v>-1.4404878129425924E-5</v>
       </c>
       <c r="I3">
-        <v>1.8671936413738877E-4</v>
+        <v>-2.683658676687628E-4</v>
       </c>
       <c r="J3">
-        <v>8.1391604908276349E-5</v>
+        <v>-1.7774384104995988E-5</v>
       </c>
       <c r="K3">
-        <v>-1.7936322838068008E-3</v>
+        <v>1.4498685777653009E-4</v>
       </c>
       <c r="L3">
-        <v>-1.9981402488156164E-7</v>
+        <v>6.5735531507016276E-7</v>
       </c>
       <c r="M3">
-        <v>1.4210649533197284E-4</v>
+        <v>6.1502563767135143E-4</v>
       </c>
       <c r="N3">
-        <v>2.3336357116932049E-5</v>
+        <v>4.5239878090796992E-5</v>
       </c>
       <c r="O3">
-        <v>1.415950246155262E-4</v>
+        <v>-6.1213696608319879E-4</v>
       </c>
       <c r="P3">
-        <v>1.6131371012306772E-5</v>
+        <v>-2.1351768737076782E-5</v>
       </c>
       <c r="Q3">
-        <v>-6.3303386923507787E-6</v>
+        <v>-5.4868098231963813E-5</v>
       </c>
       <c r="R3">
-        <v>1.3281253814056981E-5</v>
+        <v>-3.0606010113842785E-5</v>
       </c>
       <c r="S3">
-        <v>1.0248411854263395E-5</v>
+        <v>-2.3115391741157509E-5</v>
       </c>
       <c r="T3">
-        <v>1.0390991519670933E-5</v>
+        <v>-2.5573828679625876E-5</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
@@ -820,52 +820,52 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1.8277089111506939E-3</v>
+        <v>3.0578247969970107E-4</v>
       </c>
       <c r="F4">
-        <v>1.1992779036518186E-4</v>
+        <v>2.3002339730737731E-5</v>
       </c>
       <c r="G4">
-        <v>6.5459622419439256E-5</v>
+        <v>2.6296376745449379E-5</v>
       </c>
       <c r="H4">
-        <v>8.695722499396652E-5</v>
+        <v>-1.4418043065234087E-5</v>
       </c>
       <c r="I4">
-        <v>2.4649372790008783E-4</v>
+        <v>-2.7309576398693025E-4</v>
       </c>
       <c r="J4">
-        <v>8.2589387602638453E-5</v>
+        <v>-1.7910355381900445E-5</v>
       </c>
       <c r="K4">
-        <v>-1.8098275177180767E-3</v>
+        <v>1.3501898501999676E-4</v>
       </c>
       <c r="L4">
-        <v>-3.297024022685946E-7</v>
+        <v>6.6847485413745744E-7</v>
       </c>
       <c r="M4">
-        <v>2.595712139736861E-4</v>
+        <v>6.2338204588741064E-4</v>
       </c>
       <c r="N4">
-        <v>3.829047636827454E-5</v>
+        <v>4.6260556700872257E-5</v>
       </c>
       <c r="O4">
-        <v>2.5896014994941652E-4</v>
+        <v>-6.2085414538159966E-4</v>
       </c>
       <c r="P4">
-        <v>2.6551080736680888E-5</v>
+        <v>-2.2058635295252316E-5</v>
       </c>
       <c r="Q4">
-        <v>7.5186653702985495E-6</v>
+        <v>-5.0914131861645728E-5</v>
       </c>
       <c r="R4">
-        <v>2.2053527573007159E-5</v>
+        <v>-3.1243995181284845E-5</v>
       </c>
       <c r="S4">
-        <v>1.6134768884512596E-5</v>
+        <v>-2.3517693989560939E-5</v>
       </c>
       <c r="T4">
-        <v>1.6578380382270552E-5</v>
+        <v>-2.6024385078926571E-5</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.4">
@@ -882,52 +882,52 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1.8070100340992212E-3</v>
+        <v>3.1649525044485927E-4</v>
       </c>
       <c r="F5">
-        <v>1.2033853272441775E-4</v>
+        <v>2.3141519704950042E-5</v>
       </c>
       <c r="G5">
-        <v>8.2083475717809051E-5</v>
+        <v>2.6035660994239151E-5</v>
       </c>
       <c r="H5">
-        <v>8.8828041043598205E-5</v>
+        <v>-1.446830719942227E-5</v>
       </c>
       <c r="I5">
-        <v>1.5794069622643292E-4</v>
+        <v>-2.7792382752522826E-4</v>
       </c>
       <c r="J5">
-        <v>8.1184582086279988E-5</v>
+        <v>-1.8048052879748866E-5</v>
       </c>
       <c r="K5">
-        <v>-1.7982219578698277E-3</v>
+        <v>1.4916346117388457E-4</v>
       </c>
       <c r="L5">
-        <v>-7.9824232557257346E-8</v>
+        <v>6.8252472829044564E-7</v>
       </c>
       <c r="M5">
-        <v>9.2106354713905603E-5</v>
+        <v>6.3403486274182796E-4</v>
       </c>
       <c r="N5">
-        <v>1.2303705261729192E-5</v>
+        <v>4.7096800699364394E-5</v>
       </c>
       <c r="O5">
-        <v>9.1245106887072325E-5</v>
+        <v>-6.3146022148430347E-4</v>
       </c>
       <c r="P5">
-        <v>8.2515653048176318E-6</v>
+        <v>-2.2478361643152311E-5</v>
       </c>
       <c r="Q5">
-        <v>-1.0727839253377169E-5</v>
+        <v>-5.1827679271809757E-5</v>
       </c>
       <c r="R5">
-        <v>6.1535706663562451E-6</v>
+        <v>-3.1869396480033174E-5</v>
       </c>
       <c r="S5">
-        <v>6.544057214341592E-6</v>
+        <v>-2.3918439183034934E-5</v>
       </c>
       <c r="T5">
-        <v>6.7399109866528306E-6</v>
+        <v>-2.6404042728245258E-5</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.4">
@@ -944,52 +944,52 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>1.7224849434569478E-3</v>
+        <v>3.477319551166147E-4</v>
       </c>
       <c r="F6">
-        <v>1.1780745990108699E-4</v>
+        <v>2.3395081370836124E-5</v>
       </c>
       <c r="G6">
-        <v>1.1939662363147363E-4</v>
+        <v>2.6861858714255504E-5</v>
       </c>
       <c r="H6">
-        <v>9.0412089775782079E-5</v>
+        <v>-1.4691487194795627E-5</v>
       </c>
       <c r="I6">
-        <v>-1.0966332774842158E-4</v>
+        <v>-2.7781300013884902E-4</v>
       </c>
       <c r="J6">
-        <v>7.5525167630985379E-5</v>
+        <v>-1.8193573851021938E-5</v>
       </c>
       <c r="K6">
-        <v>-1.7148390179499984E-3</v>
+        <v>2.0740271429531276E-4</v>
       </c>
       <c r="L6">
-        <v>4.4709915414387069E-7</v>
+        <v>6.9563429860863835E-7</v>
       </c>
       <c r="M6">
-        <v>4.4358146260492504E-4</v>
+        <v>6.3734746072441339E-4</v>
       </c>
       <c r="N6">
-        <v>5.1874365453841165E-5</v>
+        <v>4.6766723244218156E-5</v>
       </c>
       <c r="O6">
-        <v>-4.3953544809482992E-4</v>
+        <v>-6.3420034712180495E-4</v>
       </c>
       <c r="P6">
-        <v>-3.6715908208861947E-5</v>
+        <v>-2.1782403564429842E-5</v>
       </c>
       <c r="Q6">
-        <v>-5.6829911045497283E-5</v>
+        <v>-5.860319288331084E-5</v>
       </c>
       <c r="R6">
-        <v>-3.0792249162914231E-5</v>
+        <v>-3.2015846954891458E-5</v>
       </c>
       <c r="S6">
-        <v>-1.8532498870627023E-5</v>
+        <v>-2.3819340640329756E-5</v>
       </c>
       <c r="T6">
-        <v>-1.9867797163897194E-5</v>
+        <v>-2.622286592668388E-5</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.4">
@@ -1006,52 +1006,52 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1.7073729541152716E-3</v>
+        <v>3.3989816438406706E-4</v>
       </c>
       <c r="F7">
-        <v>1.1483132402645424E-4</v>
+        <v>2.3697763026575558E-5</v>
       </c>
       <c r="G7">
-        <v>8.5847743321210146E-5</v>
+        <v>2.4545937776565552E-5</v>
       </c>
       <c r="H7">
-        <v>8.5577077697962523E-5</v>
+        <v>-1.5008748960099183E-5</v>
       </c>
       <c r="I7">
-        <v>2.7313000828144141E-5</v>
+        <v>-2.7287009288556874E-4</v>
       </c>
       <c r="J7">
-        <v>7.6568896474782377E-5</v>
+        <v>-1.8326594727113843E-5</v>
       </c>
       <c r="K7">
-        <v>-1.7049945890903473E-3</v>
+        <v>2.0117197709623724E-4</v>
       </c>
       <c r="L7">
-        <v>-8.5973468344491266E-9</v>
+        <v>6.7629832756210817E-7</v>
       </c>
       <c r="M7">
-        <v>1.8619409820530564E-4</v>
+        <v>6.2576559139415622E-4</v>
       </c>
       <c r="N7">
-        <v>6.2348872233997099E-6</v>
+        <v>4.542775423033163E-5</v>
       </c>
       <c r="O7">
-        <v>-1.8520823505241424E-4</v>
+        <v>-6.2317319680005312E-4</v>
       </c>
       <c r="P7">
-        <v>-4.4953230826649815E-6</v>
+        <v>-2.1000570995965973E-5</v>
       </c>
       <c r="Q7">
-        <v>-1.8956985513796099E-5</v>
+        <v>-5.1937287935288623E-5</v>
       </c>
       <c r="R7">
-        <v>-2.2103574792708969E-6</v>
+        <v>-3.1043262424645945E-5</v>
       </c>
       <c r="S7">
-        <v>-2.6049992811749689E-6</v>
+        <v>-2.3242830138769932E-5</v>
       </c>
       <c r="T7">
-        <v>-3.7121706100151641E-6</v>
+        <v>-2.5670460672699846E-5</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.4">
@@ -1068,52 +1068,52 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>1.7370417481288314E-3</v>
+        <v>3.2592157367616892E-4</v>
       </c>
       <c r="F8">
-        <v>1.1462288239272311E-4</v>
+        <v>2.3906715796329081E-5</v>
       </c>
       <c r="G8">
-        <v>6.3087310991249979E-5</v>
+        <v>2.2386218915926293E-5</v>
       </c>
       <c r="H8">
-        <v>8.342244109371677E-5</v>
+        <v>-1.5200683264993131E-5</v>
       </c>
       <c r="I8">
-        <v>1.7673351976554841E-4</v>
+        <v>-2.7051501092500985E-4</v>
       </c>
       <c r="J8">
-        <v>7.8606717579532415E-5</v>
+        <v>-1.8440458006807603E-5</v>
       </c>
       <c r="K8">
-        <v>-1.7268755473196507E-3</v>
+        <v>1.8040330905932933E-4</v>
       </c>
       <c r="L8">
-        <v>-2.9300505843821156E-7</v>
+        <v>6.4794949139468372E-7</v>
       </c>
       <c r="M8">
-        <v>1.1392296437406912E-4</v>
+        <v>6.1876553809270263E-4</v>
       </c>
       <c r="N8">
-        <v>3.0636470910394564E-5</v>
+        <v>4.4736319978255779E-5</v>
       </c>
       <c r="O8">
-        <v>1.13068257633131E-4</v>
+        <v>-6.166363600641489E-4</v>
       </c>
       <c r="P8">
-        <v>2.1583411580650136E-5</v>
+        <v>-2.1140789613127708E-5</v>
       </c>
       <c r="Q8">
-        <v>8.3141349023208022E-6</v>
+        <v>-4.5860557293053716E-5</v>
       </c>
       <c r="R8">
-        <v>1.8754497432382777E-5</v>
+        <v>-3.0143932235660031E-5</v>
       </c>
       <c r="S8">
-        <v>1.1175188774359412E-5</v>
+        <v>-2.296161801496055E-5</v>
       </c>
       <c r="T8">
-        <v>1.1000840459018946E-5</v>
+        <v>-2.5411587557755411E-5</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.4">
@@ -1130,52 +1130,52 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>1.7637375276535749E-3</v>
+        <v>3.2082013785839081E-4</v>
       </c>
       <c r="F9">
-        <v>1.1543364234967157E-4</v>
+        <v>2.4032891815295443E-5</v>
       </c>
       <c r="G9">
-        <v>5.9151283494429663E-5</v>
+        <v>2.3130036424845457E-5</v>
       </c>
       <c r="H9">
-        <v>8.3425045886542648E-5</v>
+        <v>-1.5255108337441925E-5</v>
       </c>
       <c r="I9">
-        <v>2.400527591817081E-4</v>
+        <v>-2.7265530661679804E-4</v>
       </c>
       <c r="J9">
-        <v>7.9781326348893344E-5</v>
+        <v>-1.8559532691142522E-5</v>
       </c>
       <c r="K9">
-        <v>-1.7463235417380929E-3</v>
+        <v>1.6748029156588018E-4</v>
       </c>
       <c r="L9">
-        <v>-3.5677095411301707E-7</v>
+        <v>6.3665373772892053E-7</v>
       </c>
       <c r="M9">
-        <v>2.4544482585042715E-4</v>
+        <v>6.2199943931773305E-4</v>
       </c>
       <c r="N9">
-        <v>4.1639672417659312E-5</v>
+        <v>4.5247295929584652E-5</v>
       </c>
       <c r="O9">
-        <v>2.4459813721477985E-4</v>
+        <v>-6.1981112230569124E-4</v>
       </c>
       <c r="P9">
-        <v>2.9420192731777206E-5</v>
+        <v>-2.1939658836345188E-5</v>
       </c>
       <c r="Q9">
-        <v>1.2308321856835391E-5</v>
+        <v>-4.6682689571753144E-5</v>
       </c>
       <c r="R9">
-        <v>2.4358130758628249E-5</v>
+        <v>-3.0112774766166694E-5</v>
       </c>
       <c r="S9">
-        <v>1.6230424080276862E-5</v>
+        <v>-2.3199669158202596E-5</v>
       </c>
       <c r="T9">
-        <v>1.6583000615355559E-5</v>
+        <v>-2.5674691642052494E-5</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.4">
@@ -1192,52 +1192,52 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1.7846727278083563E-3</v>
+        <v>3.1611925805918872E-4</v>
       </c>
       <c r="F10">
-        <v>1.1651767272269353E-4</v>
+        <v>2.3956894438015297E-5</v>
       </c>
       <c r="G10">
-        <v>6.2338709540199488E-5</v>
+        <v>2.5618584913900122E-5</v>
       </c>
       <c r="H10">
-        <v>8.4147417510394007E-5</v>
+        <v>-1.519124361948343E-5</v>
       </c>
       <c r="I10">
-        <v>2.6216855621896684E-4</v>
+        <v>-2.7307707932777703E-4</v>
       </c>
       <c r="J10">
-        <v>8.0594385508447886E-5</v>
+        <v>-1.8514023395255208E-5</v>
       </c>
       <c r="K10">
-        <v>-1.764210406690836E-3</v>
+        <v>1.5717501810286194E-4</v>
       </c>
       <c r="L10">
-        <v>-3.533841947955807E-7</v>
+        <v>6.2438402892439626E-7</v>
       </c>
       <c r="M10">
-        <v>2.928821777459234E-4</v>
+        <v>6.2297721160575747E-4</v>
       </c>
       <c r="N10">
-        <v>4.3292224290780723E-5</v>
+        <v>4.5358898205449805E-5</v>
       </c>
       <c r="O10">
-        <v>2.9227804043330252E-4</v>
+        <v>-6.2037206953391433E-4</v>
       </c>
       <c r="P10">
-        <v>3.0562932806788012E-5</v>
+        <v>-2.2296171664493158E-5</v>
       </c>
       <c r="Q10">
-        <v>6.6594238887773827E-6</v>
+        <v>-5.1910723414039239E-5</v>
       </c>
       <c r="R10">
-        <v>2.4701497750356793E-5</v>
+        <v>-2.9885402909712866E-5</v>
       </c>
       <c r="S10">
-        <v>1.7583364751772024E-5</v>
+        <v>-2.3332731871050783E-5</v>
       </c>
       <c r="T10">
-        <v>1.8164791981689632E-5</v>
+        <v>-2.5829693186096847E-5</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.4">
@@ -1254,52 +1254,52 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>1.8021839205175638E-3</v>
+        <v>3.0509202042594552E-4</v>
       </c>
       <c r="F11">
-        <v>1.1766596435336396E-4</v>
+        <v>2.3709808374405839E-5</v>
       </c>
       <c r="G11">
-        <v>6.6172397055197507E-5</v>
+        <v>2.723547731875442E-5</v>
       </c>
       <c r="H11">
-        <v>8.5043924627825618E-5</v>
+        <v>-1.5106463251868263E-5</v>
       </c>
       <c r="I11">
-        <v>2.68461590167135E-4</v>
+        <v>-2.6610022177919745E-4</v>
       </c>
       <c r="J11">
-        <v>8.1318459706380963E-5</v>
+        <v>-1.8264363461639732E-5</v>
       </c>
       <c r="K11">
-        <v>-1.7808470875024796E-3</v>
+        <v>1.4673118130303919E-4</v>
       </c>
       <c r="L11">
-        <v>-3.4367045032013266E-7</v>
+        <v>6.0233338672333048E-7</v>
       </c>
       <c r="M11">
-        <v>3.0685204546898603E-4</v>
+        <v>6.0966011369600892E-4</v>
       </c>
       <c r="N11">
-        <v>4.2598789150360972E-5</v>
+        <v>4.3894342525163665E-5</v>
       </c>
       <c r="O11">
-        <v>3.0633833375759423E-4</v>
+        <v>-6.0663965996354818E-4</v>
       </c>
       <c r="P11">
-        <v>2.9959714083815925E-5</v>
+        <v>-2.1416641175164841E-5</v>
       </c>
       <c r="Q11">
-        <v>6.8916551754227839E-7</v>
+        <v>-5.6172968470491469E-5</v>
       </c>
       <c r="R11">
-        <v>2.4057018890744075E-5</v>
+        <v>-2.8817945349146612E-5</v>
       </c>
       <c r="S11">
-        <v>1.7734950233716518E-5</v>
+        <v>-2.2768039343645796E-5</v>
       </c>
       <c r="T11">
-        <v>1.8393806385574862E-5</v>
+        <v>-2.5250090402550995E-5</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.4">
@@ -1316,52 +1316,52 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>1.8184509826824069E-3</v>
+        <v>2.9192559304647148E-4</v>
       </c>
       <c r="F12">
-        <v>1.1877940414706245E-4</v>
+        <v>2.3466624043066986E-5</v>
       </c>
       <c r="G12">
-        <v>6.8068307882640511E-5</v>
+        <v>2.7859681722475216E-5</v>
       </c>
       <c r="H12">
-        <v>8.5890336777083576E-5</v>
+        <v>-1.5034892385301646E-5</v>
       </c>
       <c r="I12">
-        <v>2.731022541411221E-4</v>
+        <v>-2.5664409622550011E-4</v>
       </c>
       <c r="J12">
-        <v>8.2044352893717587E-5</v>
+        <v>-1.8007807739195414E-5</v>
       </c>
       <c r="K12">
-        <v>-1.7965371953323483E-3</v>
+        <v>1.3630188186652958E-4</v>
       </c>
       <c r="L12">
-        <v>-3.4604377674440912E-7</v>
+        <v>5.9441174471430713E-7</v>
       </c>
       <c r="M12">
-        <v>3.1666964059695601E-4</v>
+        <v>5.9084169333800673E-4</v>
       </c>
       <c r="N12">
-        <v>4.2274637962691486E-5</v>
+        <v>4.2268871766282246E-5</v>
       </c>
       <c r="O12">
-        <v>3.161554632242769E-4</v>
+        <v>-5.8757537044584751E-4</v>
       </c>
       <c r="P12">
-        <v>2.9486625862773508E-5</v>
+        <v>-2.0088134988327511E-5</v>
       </c>
       <c r="Q12">
-        <v>-1.6560230733375647E-6</v>
+        <v>-5.8002267905976623E-5</v>
       </c>
       <c r="R12">
-        <v>2.3864018658059649E-5</v>
+        <v>-2.8018392185913399E-5</v>
       </c>
       <c r="S12">
-        <v>1.7962076526600868E-5</v>
+        <v>-2.2019705284037627E-5</v>
       </c>
       <c r="T12">
-        <v>1.86599136213772E-5</v>
+        <v>-2.4455959646729752E-5</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.4">
@@ -1378,52 +1378,52 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1.8342607654631138E-3</v>
+        <v>2.8840408776886761E-4</v>
       </c>
       <c r="F13">
-        <v>1.1977562098763883E-4</v>
+        <v>2.3371179850073531E-5</v>
       </c>
       <c r="G13">
-        <v>6.701288657495752E-5</v>
+        <v>2.7825401048175991E-5</v>
       </c>
       <c r="H13">
-        <v>8.6581931100226939E-5</v>
+        <v>-1.4920561625331175E-5</v>
       </c>
       <c r="I13">
-        <v>2.8096241294406354E-4</v>
+        <v>-2.5668638409115374E-4</v>
       </c>
       <c r="J13">
-        <v>8.2762555393856019E-5</v>
+        <v>-1.7977921743295155E-5</v>
       </c>
       <c r="K13">
-        <v>-1.8113757250830531E-3</v>
+        <v>1.2850975326728076E-4</v>
       </c>
       <c r="L13">
-        <v>-3.5722905522561632E-7</v>
+        <v>6.1901829440103029E-7</v>
       </c>
       <c r="M13">
-        <v>3.3251161221414804E-4</v>
+        <v>5.9025094378739595E-4</v>
       </c>
       <c r="N13">
-        <v>4.3153599108336493E-5</v>
+        <v>4.289785647415556E-5</v>
       </c>
       <c r="O13">
-        <v>3.3198381424881518E-4</v>
+        <v>-5.8709224686026573E-4</v>
       </c>
       <c r="P13">
-        <v>2.9870980142732151E-5</v>
+        <v>-2.0117109670536593E-5</v>
       </c>
       <c r="Q13">
-        <v>1.5235731325446977E-6</v>
+        <v>-5.6819251767592505E-5</v>
       </c>
       <c r="R13">
-        <v>2.4360420866287313E-5</v>
+        <v>-2.8830276278313249E-5</v>
       </c>
       <c r="S13">
-        <v>1.8665354218683206E-5</v>
+        <v>-2.2146221454022452E-5</v>
       </c>
       <c r="T13">
-        <v>1.9404315025894903E-5</v>
+        <v>-2.4583390768384561E-5</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.4">
@@ -1440,52 +1440,52 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>1.8499101279303432E-3</v>
+        <v>2.9384170193225145E-4</v>
       </c>
       <c r="F14">
-        <v>1.207149398396723E-4</v>
+        <v>2.3386803150060587E-5</v>
       </c>
       <c r="G14">
-        <v>6.4532396208960563E-5</v>
+        <v>2.7214828151045367E-5</v>
       </c>
       <c r="H14">
-        <v>8.7197367975022644E-5</v>
+        <v>-1.4788373846386094E-5</v>
       </c>
       <c r="I14">
-        <v>2.8981576906517148E-4</v>
+        <v>-2.6523772976361215E-4</v>
       </c>
       <c r="J14">
-        <v>8.3478014857973903E-5</v>
+        <v>-1.8105742128682323E-5</v>
       </c>
       <c r="K14">
-        <v>-1.8259271746501327E-3</v>
+        <v>1.2349590542726219E-4</v>
       </c>
       <c r="L14">
-        <v>-3.7031679767096648E-7</v>
+        <v>6.5471692778373836E-7</v>
       </c>
       <c r="M14">
-        <v>3.501389583107084E-4</v>
+        <v>6.0672813560813665E-4</v>
       </c>
       <c r="N14">
-        <v>4.4650427298620343E-5</v>
+        <v>4.5033793867332861E-5</v>
       </c>
       <c r="O14">
-        <v>3.4951564157381654E-4</v>
+        <v>-6.0391623992472887E-4</v>
       </c>
       <c r="P14">
-        <v>3.0769580916967243E-5</v>
+        <v>-2.1284051399561577E-5</v>
       </c>
       <c r="Q14">
-        <v>7.4069457696168683E-6</v>
+        <v>-5.3649007895728573E-5</v>
       </c>
       <c r="R14">
-        <v>2.5179682779707946E-5</v>
+        <v>-3.0478444386972114E-5</v>
       </c>
       <c r="S14">
-        <v>1.9525052266544662E-5</v>
+        <v>-2.2933909349376336E-5</v>
       </c>
       <c r="T14">
-        <v>2.0319381292210892E-5</v>
+        <v>-2.5418421500944532E-5</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.4">
@@ -1502,52 +1502,52 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1.8235370516777039E-3</v>
+        <v>3.078574372921139E-4</v>
       </c>
       <c r="F15">
-        <v>1.2125117791583762E-4</v>
+        <v>2.3437136405846104E-5</v>
       </c>
       <c r="G15">
-        <v>8.3360391727183014E-5</v>
+        <v>2.7159860110259615E-5</v>
       </c>
       <c r="H15">
-        <v>8.9428482169751078E-5</v>
+        <v>-1.4731297596881632E-5</v>
       </c>
       <c r="I15">
-        <v>1.7755648877937347E-4</v>
+        <v>-2.7261642389930785E-4</v>
       </c>
       <c r="J15">
-        <v>8.188033098122105E-5</v>
+        <v>-1.8215892851003446E-5</v>
       </c>
       <c r="K15">
-        <v>-1.8129567615687847E-3</v>
+        <v>1.4042374095879495E-4</v>
       </c>
       <c r="L15">
-        <v>-8.6882835148571758E-8</v>
+        <v>6.8521694629453123E-7</v>
       </c>
       <c r="M15">
-        <v>1.3401097385212779E-4</v>
+        <v>6.2286626780405641E-4</v>
       </c>
       <c r="N15">
-        <v>1.3980640687805135E-5</v>
+        <v>4.6532510168617591E-5</v>
       </c>
       <c r="O15">
-        <v>1.3317061529960483E-4</v>
+        <v>-6.2001933110877872E-4</v>
       </c>
       <c r="P15">
-        <v>9.070079613593407E-6</v>
+        <v>-2.1904937966610305E-5</v>
       </c>
       <c r="Q15">
-        <v>-1.2717983736365568E-5</v>
+        <v>-5.4618383728666231E-5</v>
       </c>
       <c r="R15">
-        <v>6.6652119130594656E-6</v>
+        <v>-3.1742114515509456E-5</v>
       </c>
       <c r="S15">
-        <v>7.9234141594497487E-6</v>
+        <v>-2.3563214199384674E-5</v>
       </c>
       <c r="T15">
-        <v>8.2925826063728891E-6</v>
+        <v>-2.6036252165795304E-5</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.4">
@@ -1564,52 +1564,52 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1.735659665428102E-3</v>
+        <v>3.4074435825459659E-4</v>
       </c>
       <c r="F16">
-        <v>1.1872091272380203E-4</v>
+        <v>2.3606013201060705E-5</v>
       </c>
       <c r="G16">
-        <v>1.2091574899386615E-4</v>
+        <v>2.8027989174006507E-5</v>
       </c>
       <c r="H16">
-        <v>9.1087895270902663E-5</v>
+        <v>-1.4866658602841198E-5</v>
       </c>
       <c r="I16">
-        <v>-1.0037491301773116E-4</v>
+        <v>-2.7424687868915498E-4</v>
       </c>
       <c r="J16">
-        <v>7.6140982855577022E-5</v>
+        <v>-1.832280213420745E-5</v>
       </c>
       <c r="K16">
-        <v>-1.728530740365386E-3</v>
+        <v>2.0027428399771452E-4</v>
       </c>
       <c r="L16">
-        <v>4.4769603846361861E-7</v>
+        <v>7.079562465150957E-7</v>
       </c>
       <c r="M16">
-        <v>4.2396271601319313E-4</v>
+        <v>6.299177766777575E-4</v>
       </c>
       <c r="N16">
-        <v>5.1797775086015463E-5</v>
+        <v>4.6603101509390399E-5</v>
       </c>
       <c r="O16">
-        <v>-4.1950040031224489E-4</v>
+        <v>-6.2649848405271769E-4</v>
       </c>
       <c r="P16">
-        <v>-3.6840330722043291E-5</v>
+        <v>-2.1320540326996706E-5</v>
       </c>
       <c r="Q16">
-        <v>-5.8667315897764638E-5</v>
+        <v>-6.1142265622038394E-5</v>
       </c>
       <c r="R16">
-        <v>-3.0939962016418576E-5</v>
+        <v>-3.2259053114103153E-5</v>
       </c>
       <c r="S16">
-        <v>-1.7942422346095555E-5</v>
+        <v>-2.3615282771061175E-5</v>
       </c>
       <c r="T16">
-        <v>-1.9196822904632427E-5</v>
+        <v>-2.6012246962636709E-5</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.4">
@@ -1626,52 +1626,52 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1.7203285824507475E-3</v>
+        <v>3.3448226167820394E-4</v>
       </c>
       <c r="F17">
-        <v>1.1571845243452117E-4</v>
+        <v>2.3828073608456179E-5</v>
       </c>
       <c r="G17">
-        <v>8.7226653704419732E-5</v>
+        <v>2.5657476726337336E-5</v>
       </c>
       <c r="H17">
-        <v>8.6256033682730049E-5</v>
+        <v>-1.5109285413927864E-5</v>
       </c>
       <c r="I17">
-        <v>3.1561226933263242E-5</v>
+        <v>-2.7051210054196417E-4</v>
       </c>
       <c r="J17">
-        <v>7.7140502980910242E-5</v>
+        <v>-1.8412123608868569E-5</v>
       </c>
       <c r="K17">
-        <v>-1.717825885862112E-3</v>
+        <v>1.9504685769788921E-4</v>
       </c>
       <c r="L17">
-        <v>-5.7457545388217568E-9</v>
+        <v>6.9301182747949497E-7</v>
       </c>
       <c r="M17">
-        <v>1.7721140466164798E-4</v>
+        <v>6.2084180535748601E-4</v>
       </c>
       <c r="N17">
-        <v>6.4873793235165067E-6</v>
+        <v>4.5487955503631383E-5</v>
       </c>
       <c r="O17">
-        <v>-1.7602219304535538E-4</v>
+        <v>-6.1804550932720304E-4</v>
       </c>
       <c r="P17">
-        <v>-4.873279067396652E-6</v>
+        <v>-2.0624831449822523E-5</v>
       </c>
       <c r="Q17">
-        <v>-2.0356033928692341E-5</v>
+        <v>-5.4119074775371701E-5</v>
       </c>
       <c r="R17">
-        <v>-2.5234207896573935E-6</v>
+        <v>-3.1468334782402962E-5</v>
       </c>
       <c r="S17">
-        <v>-2.3876671093603363E-6</v>
+        <v>-2.3139538825489581E-5</v>
       </c>
       <c r="T17">
-        <v>-3.4597096600919031E-6</v>
+        <v>-2.5563926101312973E-5</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.4">
@@ -1688,52 +1688,52 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>1.7492086626589298E-3</v>
+        <v>3.2175201340578496E-4</v>
       </c>
       <c r="F18">
-        <v>1.1547583562787622E-4</v>
+        <v>2.3962837076396681E-5</v>
       </c>
       <c r="G18">
-        <v>6.4331143221352249E-5</v>
+        <v>2.3397038603434339E-5</v>
       </c>
       <c r="H18">
-        <v>8.4088453149888664E-5</v>
+        <v>-1.5237743355100974E-5</v>
       </c>
       <c r="I18">
-        <v>1.7802411457523704E-4</v>
+        <v>-2.6899907970800996E-4</v>
       </c>
       <c r="J18">
-        <v>7.9143646871671081E-5</v>
+        <v>-1.8482036466593854E-5</v>
       </c>
       <c r="K18">
-        <v>-1.7389364074915648E-3</v>
+        <v>1.7497550288680941E-4</v>
       </c>
       <c r="L18">
-        <v>-2.8882635660920641E-7</v>
+        <v>6.6565468159751617E-7</v>
       </c>
       <c r="M18">
-        <v>1.1666327918646857E-4</v>
+        <v>6.1557977460324764E-4</v>
       </c>
       <c r="N18">
-        <v>3.0065662940614857E-5</v>
+        <v>4.4905074901180342E-5</v>
       </c>
       <c r="O18">
-        <v>1.1590122448978946E-4</v>
+        <v>-6.133022834546864E-4</v>
       </c>
       <c r="P18">
-        <v>2.1101579477544874E-5</v>
+        <v>-2.0842111553065479E-5</v>
       </c>
       <c r="Q18">
-        <v>7.2396314862999134E-6</v>
+        <v>-4.767854989040643E-5</v>
       </c>
       <c r="R18">
-        <v>1.8370910765952431E-5</v>
+        <v>-3.0631708796136081E-5</v>
       </c>
       <c r="S18">
-        <v>1.1172045560670085E-5</v>
+        <v>-2.2924010409042239E-5</v>
       </c>
       <c r="T18">
-        <v>1.1008045476046391E-5</v>
+        <v>-2.5372633899678476E-5</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.4">
@@ -1750,52 +1750,52 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>1.7749880207702518E-3</v>
+        <v>3.1754237716086209E-4</v>
       </c>
       <c r="F19">
-        <v>1.1624897888395935E-4</v>
+        <v>2.4024717276915908E-5</v>
       </c>
       <c r="G19">
-        <v>6.0255082644289359E-5</v>
+        <v>2.402331301709637E-5</v>
       </c>
       <c r="H19">
-        <v>8.4066989074926823E-5</v>
+        <v>-1.5239800632116385E-5</v>
       </c>
       <c r="I19">
-        <v>2.397121861577034E-4</v>
+        <v>-2.7172497357241809E-4</v>
       </c>
       <c r="J19">
-        <v>8.0289733887184411E-5</v>
+        <v>-1.8560940588940866E-5</v>
       </c>
       <c r="K19">
-        <v>-1.7576945247128606E-3</v>
+        <v>1.6254714864771813E-4</v>
       </c>
       <c r="L19">
-        <v>-3.5226071304350626E-7</v>
+        <v>6.5345170696673449E-7</v>
       </c>
       <c r="M19">
-        <v>2.4472025688737631E-4</v>
+        <v>6.2003300990909338E-4</v>
       </c>
       <c r="N19">
-        <v>4.1013689042301849E-5</v>
+        <v>4.5462435082299635E-5</v>
       </c>
       <c r="O19">
-        <v>2.4391875194851309E-4</v>
+        <v>-6.1772385379299521E-4</v>
       </c>
       <c r="P19">
-        <v>2.8923896024934947E-5</v>
+        <v>-2.1710313376388513E-5</v>
       </c>
       <c r="Q19">
-        <v>1.1493756574054714E-5</v>
+        <v>-4.8163525207201019E-5</v>
       </c>
       <c r="R19">
-        <v>2.397072603343986E-5</v>
+        <v>-3.0595951102441177E-5</v>
       </c>
       <c r="S19">
-        <v>1.6110398064483888E-5</v>
+        <v>-2.3203756427392364E-5</v>
       </c>
       <c r="T19">
-        <v>1.6460107872262597E-5</v>
+        <v>-2.567845513112843E-5</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.4">
@@ -1812,52 +1812,52 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>1.7951563932001591E-3</v>
+        <v>3.1347954063676298E-4</v>
       </c>
       <c r="F20">
-        <v>1.1729481775546446E-4</v>
+        <v>2.3895387130323797E-5</v>
       </c>
       <c r="G20">
-        <v>6.3314830185845494E-5</v>
+        <v>2.6394605811219662E-5</v>
       </c>
       <c r="H20">
-        <v>8.4760671597905457E-5</v>
+        <v>-1.5133950000745244E-5</v>
       </c>
       <c r="I20">
-        <v>2.6097198133356869E-4</v>
+        <v>-2.7255190070718527E-4</v>
       </c>
       <c r="J20">
-        <v>8.1077625509351492E-5</v>
+        <v>-1.8480917788110673E-5</v>
       </c>
       <c r="K20">
-        <v>-1.7749567050486803E-3</v>
+        <v>1.5260474174283445E-4</v>
       </c>
       <c r="L20">
-        <v>-3.4900517675851006E-7</v>
+        <v>6.3935766547729145E-7</v>
       </c>
       <c r="M20">
-        <v>2.9033829923719168E-4</v>
+        <v>6.2185956630855799E-4</v>
       </c>
       <c r="N20">
-        <v>4.267266922397539E-5</v>
+        <v>4.55878434877377E-5</v>
       </c>
       <c r="O20">
-        <v>2.8975302120670676E-4</v>
+        <v>-6.1914807884022593E-4</v>
       </c>
       <c r="P20">
-        <v>3.0090202926658094E-5</v>
+        <v>-2.2127769625512883E-5</v>
       </c>
       <c r="Q20">
-        <v>6.0466418290161528E-6</v>
+        <v>-5.3095965995453298E-5</v>
       </c>
       <c r="R20">
-        <v>2.4338045477634296E-5</v>
+        <v>-3.0329851142596453E-5</v>
       </c>
       <c r="S20">
-        <v>1.740564766805619E-5</v>
+        <v>-2.3362330466625281E-5</v>
       </c>
       <c r="T20">
-        <v>1.7977648894884624E-5</v>
+        <v>-2.5859493689495139E-5</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.4">
@@ -1874,52 +1874,52 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>1.8120297463610768E-3</v>
+        <v>3.0289622372947633E-4</v>
       </c>
       <c r="F21">
-        <v>1.1840558727271855E-4</v>
+        <v>2.3605411115568131E-5</v>
       </c>
       <c r="G21">
-        <v>6.7042630689684302E-5</v>
+        <v>2.7903768568648957E-5</v>
       </c>
       <c r="H21">
-        <v>8.5627572843804955E-5</v>
+        <v>-1.5016359611763619E-5</v>
       </c>
       <c r="I21">
-        <v>2.6683873147703707E-4</v>
+        <v>-2.6585438172332942E-4</v>
       </c>
       <c r="J21">
-        <v>8.1778278399724513E-5</v>
+        <v>-1.8202910723630339E-5</v>
       </c>
       <c r="K21">
-        <v>-1.7910203896462917E-3</v>
+        <v>1.4243931218516082E-4</v>
       </c>
       <c r="L21">
-        <v>-3.3956118272726599E-7</v>
+        <v>6.1516425375884864E-7</v>
       </c>
       <c r="M21">
-        <v>3.0340306693688035E-4</v>
+        <v>6.0912617482244968E-4</v>
       </c>
       <c r="N21">
-        <v>4.2007857700809836E-5</v>
+        <v>4.4122127292212099E-5</v>
       </c>
       <c r="O21">
-        <v>3.0289607821032405E-4</v>
+        <v>-6.060138694010675E-4</v>
       </c>
       <c r="P21">
-        <v>2.9520104362745769E-5</v>
+        <v>-2.1300536900525913E-5</v>
       </c>
       <c r="Q21">
-        <v>2.2468280747034441E-7</v>
+        <v>-5.7109184126602486E-5</v>
       </c>
       <c r="R21">
-        <v>2.3723179765511304E-5</v>
+        <v>-2.9209752028691582E-5</v>
       </c>
       <c r="S21">
-        <v>1.7531323464936577E-5</v>
+        <v>-2.2812542738392949E-5</v>
       </c>
       <c r="T21">
-        <v>1.8177852325607091E-5</v>
+        <v>-2.5295052182627842E-5</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.4">
@@ -1936,52 +1936,52 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1.8277356866747141E-3</v>
+        <v>2.9005686519667506E-4</v>
       </c>
       <c r="F22">
-        <v>1.1948264727834612E-4</v>
+        <v>2.3328791940002702E-5</v>
       </c>
       <c r="G22">
-        <v>6.8855471909046173E-5</v>
+        <v>2.8433960324036889E-5</v>
       </c>
       <c r="H22">
-        <v>8.6445033957716078E-5</v>
+        <v>-1.4919793102308176E-5</v>
       </c>
       <c r="I22">
-        <v>2.7128300280310214E-4</v>
+        <v>-2.5659028324298561E-4</v>
       </c>
       <c r="J22">
-        <v>8.2481768913567066E-5</v>
+        <v>-1.7923899576999247E-5</v>
       </c>
       <c r="K22">
-        <v>-1.8061789451166987E-3</v>
+        <v>1.3223435962572694E-4</v>
       </c>
       <c r="L22">
-        <v>-3.4220025213471672E-7</v>
+        <v>6.051180889699026E-7</v>
       </c>
       <c r="M22">
-        <v>3.1280503026209772E-4</v>
+        <v>5.9070688439533114E-4</v>
       </c>
       <c r="N22">
-        <v>4.1716160922078416E-5</v>
+        <v>4.2489340557949618E-5</v>
       </c>
       <c r="O22">
-        <v>3.1229457817971706E-4</v>
+        <v>-5.8736500795930624E-4</v>
       </c>
       <c r="P22">
-        <v>2.9078124498482794E-5</v>
+        <v>-2.0015871996292844E-5</v>
       </c>
       <c r="Q22">
-        <v>-2.017725137193338E-6</v>
+        <v>-5.8735091442940757E-5</v>
       </c>
       <c r="R22">
-        <v>2.3556574888061732E-5</v>
+        <v>-2.8355087124509737E-5</v>
       </c>
       <c r="S22">
-        <v>1.7748860045685433E-5</v>
+        <v>-2.2072288629715331E-5</v>
       </c>
       <c r="T22">
-        <v>1.8433351215207949E-5</v>
+        <v>-2.4509137801942416E-5</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.4">
@@ -1998,52 +1998,52 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>1.8430298659950495E-3</v>
+        <v>2.8681312687695026E-4</v>
       </c>
       <c r="F23">
-        <v>1.2044382310705259E-4</v>
+        <v>2.3208371203509159E-5</v>
       </c>
       <c r="G23">
-        <v>6.7736713390331715E-5</v>
+        <v>2.8320260753389448E-5</v>
       </c>
       <c r="H23">
-        <v>8.7108885054476559E-5</v>
+        <v>-1.4786978681513574E-5</v>
       </c>
       <c r="I23">
-        <v>2.7906641480512917E-4</v>
+        <v>-2.5676217046566308E-4</v>
       </c>
       <c r="J23">
-        <v>8.3178310887888074E-5</v>
+        <v>-1.7876789570436813E-5</v>
       </c>
       <c r="K23">
-        <v>-1.8205199157819152E-3</v>
+        <v>1.2463117309380323E-4</v>
       </c>
       <c r="L23">
-        <v>-3.5360787364879798E-7</v>
+        <v>6.2778366327620461E-7</v>
       </c>
       <c r="M23">
-        <v>3.2848445698618889E-4</v>
+        <v>5.9038132894784212E-4</v>
       </c>
       <c r="N23">
-        <v>4.2624615161912516E-5</v>
+        <v>4.3105163058498874E-5</v>
       </c>
       <c r="O23">
-        <v>3.2796358573250473E-4</v>
+        <v>-5.8716570492833853E-4</v>
       </c>
       <c r="P23">
-        <v>2.9488470318028703E-5</v>
+        <v>-2.0080506146769039E-5</v>
       </c>
       <c r="Q23">
-        <v>1.2283464911888586E-6</v>
+        <v>-5.7389879657421261E-5</v>
       </c>
       <c r="R23">
-        <v>2.4074193788692355E-5</v>
+        <v>-2.911503725044895E-5</v>
       </c>
       <c r="S23">
-        <v>1.8450573406880721E-5</v>
+        <v>-2.2202459149411879E-5</v>
       </c>
       <c r="T23">
-        <v>1.9176060959580354E-5</v>
+        <v>-2.464027056703344E-5</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.4">
@@ -2060,52 +2060,52 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>1.8582009943202138E-3</v>
+        <v>2.9248493956401944E-4</v>
       </c>
       <c r="F24">
-        <v>1.2134955613873899E-4</v>
+        <v>2.3206048354040831E-5</v>
       </c>
       <c r="G24">
-        <v>6.520822353195399E-5</v>
+        <v>2.7644031433737837E-5</v>
       </c>
       <c r="H24">
-        <v>8.7697910203132778E-5</v>
+        <v>-1.4641630514233839E-5</v>
       </c>
       <c r="I24">
-        <v>2.8790609212592244E-4</v>
+        <v>-2.6539684040471911E-4</v>
       </c>
       <c r="J24">
-        <v>8.3872859249822795E-5</v>
+        <v>-1.7991813365370035E-5</v>
       </c>
       <c r="K24">
-        <v>-1.8346031429246068E-3</v>
+        <v>1.1978213296970353E-4</v>
       </c>
       <c r="L24">
-        <v>-3.6687526971945772E-7</v>
+        <v>6.61790238609683E-7</v>
       </c>
       <c r="M24">
-        <v>3.4608485293574631E-4</v>
+        <v>6.070274394005537E-4</v>
       </c>
       <c r="N24">
-        <v>4.4147025619167835E-5</v>
+        <v>4.5223816414363682E-5</v>
       </c>
       <c r="O24">
-        <v>3.4547157702036202E-4</v>
+        <v>-6.041752640157938E-4</v>
       </c>
       <c r="P24">
-        <v>3.0408431484829634E-5</v>
+        <v>-2.1275458493619226E-5</v>
       </c>
       <c r="Q24">
-        <v>7.1510630732518621E-6</v>
+        <v>-5.4092757636681199E-5</v>
       </c>
       <c r="R24">
-        <v>2.4910224965424277E-5</v>
+        <v>-3.0716815672349185E-5</v>
       </c>
       <c r="S24">
-        <v>1.9312801669002511E-5</v>
+        <v>-2.299086372659076E-5</v>
       </c>
       <c r="T24">
-        <v>2.0093975763302296E-5</v>
+        <v>-2.5475979782640934E-5</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.4">
@@ -2122,52 +2122,52 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>1.8315532943233848E-3</v>
+        <v>3.0646167579106987E-4</v>
       </c>
       <c r="F25">
-        <v>1.2185438390588388E-4</v>
+        <v>2.3243850591825321E-5</v>
       </c>
       <c r="G25">
-        <v>8.4003833762835711E-5</v>
+        <v>2.7535063054529019E-5</v>
       </c>
       <c r="H25">
-        <v>8.9904053311329335E-5</v>
+        <v>-1.4575628483726177E-5</v>
       </c>
       <c r="I25">
-        <v>1.7562966968398541E-4</v>
+        <v>-2.7282588416710496E-4</v>
       </c>
       <c r="J25">
-        <v>8.2254147855564952E-5</v>
+        <v>-1.8092825484927744E-5</v>
       </c>
       <c r="K25">
-        <v>-1.8211768474429846E-3</v>
+        <v>1.3684522127732635E-4</v>
       </c>
       <c r="L25">
-        <v>-8.3512361470639007E-8</v>
+        <v>6.908598493282625E-7</v>
       </c>
       <c r="M25">
-        <v>1.2997791054658592E-4</v>
+        <v>6.2327104387804866E-4</v>
       </c>
       <c r="N25">
-        <v>1.3496384781319648E-5</v>
+        <v>4.6705619752174243E-5</v>
       </c>
       <c r="O25">
-        <v>1.2910019722767174E-4</v>
+        <v>-6.2039348995313048E-4</v>
       </c>
       <c r="P25">
-        <v>8.7202051872736774E-6</v>
+        <v>-2.1917914637015201E-5</v>
       </c>
       <c r="Q25">
-        <v>-1.2958318620803766E-5</v>
+        <v>-5.4961750720394775E-5</v>
       </c>
       <c r="R25">
-        <v>6.4038963500934187E-6</v>
+        <v>-3.1940493499860168E-5</v>
       </c>
       <c r="S25">
-        <v>7.7121940194047056E-6</v>
+        <v>-2.3619015337317251E-5</v>
       </c>
       <c r="T25">
-        <v>8.068489478318952E-6</v>
+        <v>-2.609262264741119E-5</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.4">
@@ -2184,52 +2184,52 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1.743584405630827E-3</v>
+        <v>3.3894804073497653E-4</v>
       </c>
       <c r="F26">
-        <v>1.1929292668355629E-4</v>
+        <v>2.3404507373925298E-5</v>
       </c>
       <c r="G26">
-        <v>1.2148326641181484E-4</v>
+        <v>2.8359596399241127E-5</v>
       </c>
       <c r="H26">
-        <v>9.1534573584794998E-5</v>
+        <v>-1.470551887905458E-5</v>
       </c>
       <c r="I26">
-        <v>-1.0200797987636179E-4</v>
+        <v>-2.7448523906059563E-4</v>
       </c>
       <c r="J26">
-        <v>7.6498508860822767E-5</v>
+        <v>-1.8193710275227204E-5</v>
       </c>
       <c r="K26">
-        <v>-1.7363532679155469E-3</v>
+        <v>1.9682318088598549E-4</v>
       </c>
       <c r="L26">
-        <v>4.5030904516352166E-7</v>
+        <v>7.1242669719140395E-7</v>
       </c>
       <c r="M26">
-        <v>4.2744918027892709E-4</v>
+        <v>6.303866975940764E-4</v>
       </c>
       <c r="N26">
-        <v>5.2200201025698334E-5</v>
+        <v>4.6761131670791656E-5</v>
       </c>
       <c r="O26">
-        <v>-4.2299155029468238E-4</v>
+        <v>-6.2694185180589557E-4</v>
       </c>
       <c r="P26">
-        <v>-3.7130019336473197E-5</v>
+        <v>-2.134983878931962E-5</v>
       </c>
       <c r="Q26">
-        <v>-5.8843575970968232E-5</v>
+        <v>-6.140898767625913E-5</v>
       </c>
       <c r="R26">
-        <v>-3.1150255381362513E-5</v>
+        <v>-3.2424166420241818E-5</v>
       </c>
       <c r="S26">
-        <v>-1.812186928873416E-5</v>
+        <v>-2.3669017537031323E-5</v>
       </c>
       <c r="T26">
-        <v>-1.9387740394449793E-5</v>
+        <v>-2.6066478312714025E-5</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.4">
@@ -2246,52 +2246,52 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>1.7277743900194764E-3</v>
+        <v>3.3277811598964036E-4</v>
       </c>
       <c r="F27">
-        <v>1.1626124614849687E-4</v>
+        <v>2.3621678337804042E-5</v>
       </c>
       <c r="G27">
-        <v>8.7749584054108709E-5</v>
+        <v>2.5953826479963027E-5</v>
       </c>
       <c r="H27">
-        <v>8.6679006926715374E-5</v>
+        <v>-1.4945273505873047E-5</v>
       </c>
       <c r="I27">
-        <v>3.0146658900775947E-5</v>
+        <v>-2.7076585683971643E-4</v>
       </c>
       <c r="J27">
-        <v>7.7481781772803515E-5</v>
+        <v>-1.8279422874911688E-5</v>
       </c>
       <c r="K27">
-        <v>-1.7252812394872308E-3</v>
+        <v>1.9171206804458052E-4</v>
       </c>
       <c r="L27">
-        <v>-3.4622864575339918E-9</v>
+        <v>6.9653140144509962E-7</v>
       </c>
       <c r="M27">
-        <v>1.8024496966972947E-4</v>
+        <v>6.2134239124134183E-4</v>
       </c>
       <c r="N27">
-        <v>6.8417398324527312E-6</v>
+        <v>4.5631270040757954E-5</v>
       </c>
       <c r="O27">
-        <v>-1.7905690765473992E-4</v>
+        <v>-6.1852816725149751E-4</v>
       </c>
       <c r="P27">
-        <v>-5.1293354772496969E-6</v>
+        <v>-2.0666486307163723E-5</v>
       </c>
       <c r="Q27">
-        <v>-2.0503310224739835E-5</v>
+        <v>-5.4327101679518819E-5</v>
       </c>
       <c r="R27">
-        <v>-2.7078669972979696E-6</v>
+        <v>-3.1606141419615597E-5</v>
       </c>
       <c r="S27">
-        <v>-2.5469066713412758E-6</v>
+        <v>-2.3190834326669574E-5</v>
       </c>
       <c r="T27">
-        <v>-3.6286050999478903E-6</v>
+        <v>-2.5615639970055781E-5</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.4">
@@ -2308,52 +2308,52 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>1.7561393324285746E-3</v>
+        <v>3.2025168184190989E-4</v>
       </c>
       <c r="F28">
-        <v>1.1599244317039847E-4</v>
+        <v>2.3754191715852357E-5</v>
       </c>
       <c r="G28">
-        <v>6.4848900365177542E-5</v>
+        <v>2.3665405024075881E-5</v>
       </c>
       <c r="H28">
-        <v>8.4493214671965688E-5</v>
+        <v>-1.5072678252181504E-5</v>
       </c>
       <c r="I28">
-        <v>1.7660575394984335E-4</v>
+        <v>-2.6925918064080179E-4</v>
       </c>
       <c r="J28">
-        <v>7.946736877784133E-5</v>
+        <v>-1.8347458535572514E-5</v>
       </c>
       <c r="K28">
-        <v>-1.7460327362641692E-3</v>
+        <v>1.7175734683405608E-4</v>
       </c>
       <c r="L28">
-        <v>-2.8637069249271008E-7</v>
+        <v>6.6841556645158562E-7</v>
       </c>
       <c r="M28">
-        <v>1.1364047531969845E-4</v>
+        <v>6.1609689146280289E-4</v>
       </c>
       <c r="N28">
-        <v>2.9701743187615648E-5</v>
+        <v>4.5035303628537804E-5</v>
       </c>
       <c r="O28">
-        <v>1.1288415407761931E-4</v>
+        <v>-6.138066528365016E-4</v>
       </c>
       <c r="P28">
-        <v>2.0839186618104577E-5</v>
+        <v>-2.0892832253593951E-5</v>
       </c>
       <c r="Q28">
-        <v>7.0759092523076106E-6</v>
+        <v>-4.7843874199315906E-5</v>
       </c>
       <c r="R28">
-        <v>1.8178172467742115E-5</v>
+        <v>-3.0747436539968476E-5</v>
       </c>
       <c r="S28">
-        <v>1.1011654351023026E-5</v>
+        <v>-2.2972735678195022E-5</v>
       </c>
       <c r="T28">
-        <v>1.083863025996834E-5</v>
+        <v>-2.5421710233786143E-5</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.4">
@@ -2370,52 +2370,52 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>1.7814952880144119E-3</v>
+        <v>3.1620607478544116E-4</v>
       </c>
       <c r="F29">
-        <v>1.1674061533994973E-4</v>
+        <v>2.3815957320039161E-5</v>
       </c>
       <c r="G29">
-        <v>6.0764239606214687E-5</v>
+        <v>2.426903483865317E-5</v>
       </c>
       <c r="H29">
-        <v>8.4453800809569657E-5</v>
+        <v>-1.5075099327077623E-5</v>
       </c>
       <c r="I29">
-        <v>2.3826438700780272E-4</v>
+        <v>-2.7198469615541399E-4</v>
       </c>
       <c r="J29">
-        <v>8.0596546467859298E-5</v>
+        <v>-1.8425835150992498E-5</v>
       </c>
       <c r="K29">
-        <v>-1.7644441686570644E-3</v>
+        <v>1.5944160986691713E-4</v>
       </c>
       <c r="L29">
-        <v>-3.4970312867699249E-7</v>
+        <v>6.5561613382669748E-7</v>
       </c>
       <c r="M29">
-        <v>2.4164539354387671E-4</v>
+        <v>6.2055600574240088E-4</v>
       </c>
       <c r="N29">
-        <v>4.064115637447685E-5</v>
+        <v>4.5581793528981507E-5</v>
       </c>
       <c r="O29">
-        <v>2.4085273616947234E-4</v>
+        <v>-6.1823672149330378E-4</v>
       </c>
       <c r="P29">
-        <v>2.865715759980958E-5</v>
+        <v>-2.1767251382698305E-5</v>
       </c>
       <c r="Q29">
-        <v>1.131833232648205E-5</v>
+        <v>-4.8296653403667733E-5</v>
       </c>
       <c r="R29">
-        <v>2.377258351771161E-5</v>
+        <v>-3.0693958251504228E-5</v>
       </c>
       <c r="S29">
-        <v>1.5948371583363041E-5</v>
+        <v>-2.3249820515047759E-5</v>
       </c>
       <c r="T29">
-        <v>1.6289113773382269E-5</v>
+        <v>-2.5724841179908253E-5</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.4">
@@ -2432,52 +2432,52 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>1.8013102235272527E-3</v>
+        <v>3.1227307044900954E-4</v>
       </c>
       <c r="F30">
-        <v>1.1776234896387905E-4</v>
+        <v>2.3687962311669253E-5</v>
       </c>
       <c r="G30">
-        <v>6.3806313846725971E-5</v>
+        <v>2.6621386496117339E-5</v>
       </c>
       <c r="H30">
-        <v>8.5129315266385674E-5</v>
+        <v>-1.4970676602388266E-5</v>
       </c>
       <c r="I30">
-        <v>2.5952214491553605E-4</v>
+        <v>-2.72807024884969E-4</v>
       </c>
       <c r="J30">
-        <v>8.136861288221553E-5</v>
+        <v>-1.8346319848205894E-5</v>
       </c>
       <c r="K30">
-        <v>-1.7813745653256774E-3</v>
+        <v>1.496064942330122E-4</v>
       </c>
       <c r="L30">
-        <v>-3.4645296409507864E-7</v>
+        <v>6.4105324781849049E-7</v>
       </c>
       <c r="M30">
-        <v>2.8726283926516771E-4</v>
+        <v>6.2238075770437717E-4</v>
       </c>
       <c r="N30">
-        <v>4.2304211092414334E-5</v>
+        <v>4.5698056055698544E-5</v>
       </c>
       <c r="O30">
-        <v>2.8668460436165333E-4</v>
+        <v>-6.1966065550222993E-4</v>
       </c>
       <c r="P30">
-        <v>2.9827593607478775E-5</v>
+        <v>-2.2188822185853496E-5</v>
       </c>
       <c r="Q30">
-        <v>5.8721661844174378E-6</v>
+        <v>-5.3203624702291563E-5</v>
       </c>
       <c r="R30">
-        <v>2.4141832909663208E-5</v>
+        <v>-3.0413628337555565E-5</v>
       </c>
       <c r="S30">
-        <v>1.7245167327928357E-5</v>
+        <v>-2.3405804313370027E-5</v>
       </c>
       <c r="T30">
-        <v>1.7808220945880748E-5</v>
+        <v>-2.5903271307470277E-5</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.4">
@@ -2494,52 +2494,52 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>1.817869720980525E-3</v>
+        <v>3.0178451561369002E-4</v>
       </c>
       <c r="F31">
-        <v>1.1884993000421673E-4</v>
+        <v>2.3400230929837562E-5</v>
       </c>
       <c r="G31">
-        <v>6.7511340603232384E-5</v>
+        <v>2.8114500310039148E-5</v>
       </c>
       <c r="H31">
-        <v>8.5978252172935754E-5</v>
+        <v>-1.4855285371595528E-5</v>
       </c>
       <c r="I31">
-        <v>2.6541424449533224E-4</v>
+        <v>-2.6610365603119135E-4</v>
       </c>
       <c r="J31">
-        <v>8.2054444646928459E-5</v>
+        <v>-1.8069620637106709E-5</v>
       </c>
       <c r="K31">
-        <v>-1.7971220659092069E-3</v>
+        <v>1.3954323367215693E-4</v>
       </c>
       <c r="L31">
-        <v>-3.3707337365740386E-7</v>
+        <v>6.164920023365994E-7</v>
       </c>
       <c r="M31">
-        <v>3.003812744282186E-4</v>
+        <v>6.096423021517694E-4</v>
       </c>
       <c r="N31">
-        <v>4.1651175706647336E-5</v>
+        <v>4.4224634621059522E-5</v>
       </c>
       <c r="O31">
-        <v>2.9987836023792624E-4</v>
+        <v>-6.0652289539575577E-4</v>
       </c>
       <c r="P31">
-        <v>2.9266913770698011E-5</v>
+        <v>-2.136436160071753E-5</v>
       </c>
       <c r="Q31">
-        <v>5.8935086144629167E-8</v>
+        <v>-5.719637920265086E-5</v>
       </c>
       <c r="R31">
-        <v>2.3533246348961256E-5</v>
+        <v>-2.9282178729772568E-5</v>
       </c>
       <c r="S31">
-        <v>1.7374897652189247E-5</v>
+        <v>-2.28536591748707E-5</v>
       </c>
       <c r="T31">
-        <v>1.8012620785157196E-5</v>
+        <v>-2.5336466933367774E-5</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.4">
@@ -2556,52 +2556,52 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>1.8332806648686528E-3</v>
+        <v>2.8902807389385998E-4</v>
       </c>
       <c r="F32">
-        <v>1.199047765112482E-4</v>
+        <v>2.3126658561523072E-5</v>
       </c>
       <c r="G32">
-        <v>6.9300491304602474E-5</v>
+        <v>2.8631084205699153E-5</v>
       </c>
       <c r="H32">
-        <v>8.6778338300064206E-5</v>
+        <v>-1.476147099310765E-5</v>
       </c>
       <c r="I32">
-        <v>2.6989969774149358E-4</v>
+        <v>-2.5683423154987395E-4</v>
       </c>
       <c r="J32">
-        <v>8.2743943494278938E-5</v>
+        <v>-1.7792523067328148E-5</v>
       </c>
       <c r="K32">
-        <v>-1.8119794549420476E-3</v>
+        <v>1.2943593901582062E-4</v>
       </c>
       <c r="L32">
-        <v>-3.3979640079451201E-7</v>
+        <v>6.0615650454565184E-7</v>
       </c>
       <c r="M32">
-        <v>3.0986711499281228E-4</v>
+        <v>5.9121829690411687E-4</v>
       </c>
       <c r="N32">
-        <v>4.1374230931978673E-5</v>
+        <v>4.2585332266753539E-5</v>
       </c>
       <c r="O32">
-        <v>3.093593695666641E-4</v>
+        <v>-5.8787077432498336E-4</v>
       </c>
       <c r="P32">
-        <v>2.8836302590207197E-5</v>
+        <v>-2.0081604816368781E-5</v>
       </c>
       <c r="Q32">
-        <v>-2.1728608317062026E-6</v>
+        <v>-5.8806050219573081E-5</v>
       </c>
       <c r="R32">
-        <v>2.3374432203127071E-5</v>
+        <v>-2.8418473448255099E-5</v>
       </c>
       <c r="S32">
-        <v>1.7597754776943475E-5</v>
+        <v>-2.2111362341092899E-5</v>
       </c>
       <c r="T32">
-        <v>1.8273762179887854E-5</v>
+        <v>-2.454852256050799E-5</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.4">
@@ -2618,52 +2618,52 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>1.8482909072190523E-3</v>
+        <v>2.858807856682688E-4</v>
       </c>
       <c r="F33">
-        <v>1.2084474292350933E-4</v>
+        <v>2.3010179575067014E-5</v>
       </c>
       <c r="G33">
-        <v>6.8159832153469324E-5</v>
+        <v>2.8505693990155123E-5</v>
       </c>
       <c r="H33">
-        <v>8.7425585661549121E-5</v>
+        <v>-1.4631833437306341E-5</v>
       </c>
       <c r="I33">
-        <v>2.7772987959906459E-4</v>
+        <v>-2.5700038531795144E-4</v>
       </c>
       <c r="J33">
-        <v>8.3427192294038832E-5</v>
+        <v>-1.774775046214927E-5</v>
       </c>
       <c r="K33">
-        <v>-1.8260338110849261E-3</v>
+        <v>1.2192643043817952E-4</v>
       </c>
       <c r="L33">
-        <v>-3.5128661579619802E-7</v>
+        <v>6.2858890714778681E-7</v>
       </c>
       <c r="M33">
-        <v>3.2563964487053454E-4</v>
+        <v>5.9088645502924919E-4</v>
       </c>
       <c r="N33">
-        <v>4.229763726470992E-5</v>
+        <v>4.319548315834254E-5</v>
       </c>
       <c r="O33">
-        <v>3.2512293546460569E-4</v>
+        <v>-5.87666523642838E-4</v>
       </c>
       <c r="P33">
-        <v>2.9258091672090814E-5</v>
+        <v>-2.0147270333836786E-5</v>
       </c>
       <c r="Q33">
-        <v>1.0815762152560637E-6</v>
+        <v>-5.7448218285571784E-5</v>
       </c>
       <c r="R33">
-        <v>2.3899814550532028E-5</v>
+        <v>-2.9170934794819914E-5</v>
       </c>
       <c r="S33">
-        <v>1.8305181583855301E-5</v>
+        <v>-2.2239655663724989E-5</v>
       </c>
       <c r="T33">
-        <v>1.9022434571525082E-5</v>
+        <v>-2.4677803594386205E-5</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
+++ b/inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,72 +449,312 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>ノード 6837, 1..Total Translation</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 1..Total Translation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 1..Total Translation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 1..Total Translation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ノード 484, 1..Total Translation</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 1..Total Translation</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>ノード 15858, 2..T1 Translation</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ノード 19459, 2..T1 Translation</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ノード 6837, 2..T1 Translation</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 2..T1 Translation</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 2..T1 Translation</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 2..T1 Translation</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ノード 484, 2..T1 Translation</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 2..T1 Translation</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>ノード 15858, 3..T2 Translation</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ノード 19459, 3..T2 Translation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ノード 6837, 3..T2 Translation</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 3..T2 Translation</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 3..T2 Translation</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 3..T2 Translation</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ノード 484, 3..T2 Translation</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 3..T2 Translation</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ノード 15858, 4..T3 Translation</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ノード 19459, 4..T3 Translation</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ノード 6837, 4..T3 Translation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 4..T3 Translation</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 4..T3 Translation</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 4..T3 Translation</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>ノード 484, 4..T3 Translation</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 4..T3 Translation</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ノード 15858, 5..Total Rotation</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ノード 19459, 5..Total Rotation</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>ノード 6837, 5..Total Rotation</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 5..Total Rotation</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 5..Total Rotation</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 5..Total Rotation</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>ノード 484, 5..Total Rotation</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 5..Total Rotation</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ノード 15858, 6..R1 Rotation</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>ノード 19459, 6..R1 Rotation</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>ノード 6837, 6..R1 Rotation</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 6..R1 Rotation</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 6..R1 Rotation</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 6..R1 Rotation</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>ノード 484, 6..R1 Rotation</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 6..R1 Rotation</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
         <is>
           <t>ノード 15858, 7..R2 Rotation</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>ノード 19459, 7..R2 Rotation</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>ノード 6837, 7..R2 Rotation</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 7..R2 Rotation</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 7..R2 Rotation</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 7..R2 Rotation</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>ノード 484, 7..R2 Rotation</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 7..R2 Rotation</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ノード 15858, 8..R3 Rotation</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ノード 19459, 8..R3 Rotation</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>ノード 6837, 8..R3 Rotation</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>ノード 28360, 8..R3 Rotation</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>ノード 22371, 8..R3 Rotation</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>ノード 12827, 8..R3 Rotation</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>ノード 484, 8..R3 Rotation</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>ノード 17598, 8..R3 Rotation</t>
         </is>
       </c>
     </row>
@@ -540,46 +780,190 @@
         <v>2.305287671333645e-05</v>
       </c>
       <c r="G2" t="n">
+        <v>0.0001961815723916516</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0002278955071233213</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0002487608580850065</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0001772957330103964</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0003325341967865825</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.183102333219722e-05</v>
+      </c>
+      <c r="M2" t="n">
         <v>2.713894718908705e-05</v>
       </c>
-      <c r="H2" t="n">
+      <c r="N2" t="n">
         <v>-1.453145523555577e-05</v>
       </c>
-      <c r="I2" t="n">
+      <c r="O2" t="n">
+        <v>8.585149043938145e-05</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-8.21269495645538e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.53414793103002e-07</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.0531995940255e-05</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.469178773229942e-05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-1.591384716448374e-05</v>
+      </c>
+      <c r="U2" t="n">
         <v>-0.0002688269887585193</v>
       </c>
-      <c r="J2" t="n">
+      <c r="V2" t="n">
         <v>-1.788413101166952e-05</v>
       </c>
-      <c r="K2" t="n">
+      <c r="W2" t="n">
+        <v>-9.927329665515572e-05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.0001195088698295876</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.340151629847242e-05</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.0001598354574525729</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.000297755264909938</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1.493813670094823e-05</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0.0001472437579650432</v>
       </c>
-      <c r="L2" t="n">
+      <c r="AD2" t="n">
         <v>6.555616778314288e-07</v>
       </c>
-      <c r="M2" t="n">
+      <c r="AE2" t="n">
+        <v>0.0001458133920095861</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0001758100115694106</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.0002483989810571074</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7.599655509693548e-05</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.0001439349580323324</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4.416381784722034e-07</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.0006162791978567839</v>
       </c>
-      <c r="N2" t="n">
+      <c r="AL2" t="n">
         <v>4.51962259830907e-05</v>
       </c>
-      <c r="O2" t="n">
+      <c r="AM2" t="n">
+        <v>0.0003698368964251131</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.0004150508611928672</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.0003801028069574386</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.0001707047194940969</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.0006336396909318864</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.353929762146436e-05</v>
+      </c>
+      <c r="AS2" t="n">
         <v>-0.0006133402930572629</v>
       </c>
-      <c r="P2" t="n">
+      <c r="AT2" t="n">
         <v>-2.134761234628968e-05</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AU2" t="n">
+        <v>-0.0002862701949197799</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.0002883950946852565</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-0.0003764725406654179</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-0.0001529933360870928</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.0006281866226345301</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-1.754912409523968e-05</v>
+      </c>
+      <c r="BA2" t="n">
         <v>-5.550032437895425e-05</v>
       </c>
-      <c r="R2" t="n">
+      <c r="BB2" t="n">
         <v>-3.054762419196777e-05</v>
       </c>
-      <c r="S2" t="n">
+      <c r="BC2" t="n">
+        <v>5.899381721974351e-05</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.0001539351505925879</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-4.926877591060475e-05</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-5.095614324091002e-05</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-7.683218427700922e-05</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-3.052127794944681e-05</v>
+      </c>
+      <c r="BI2" t="n">
         <v>-2.30967634706758e-05</v>
       </c>
-      <c r="T2" t="n">
+      <c r="BJ2" t="n">
         <v>-2.556992330937646e-05</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.0002266019437229261</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.0002557332045398653</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-1.786489156074822e-05</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-5.600546137429774e-05</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-3.126667070318945e-05</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-2.561542714829557e-05</v>
       </c>
     </row>
     <row r="3">
@@ -604,46 +988,190 @@
         <v>2.305287671333645e-05</v>
       </c>
       <c r="G3" t="n">
+        <v>0.0001961815723916516</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0002278955071233213</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0002487608580850065</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0001772957330103964</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0003325341967865825</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.183102333219722e-05</v>
+      </c>
+      <c r="M3" t="n">
         <v>2.713894718908705e-05</v>
       </c>
-      <c r="H3" t="n">
+      <c r="N3" t="n">
         <v>-1.453145523555577e-05</v>
       </c>
-      <c r="I3" t="n">
+      <c r="O3" t="n">
+        <v>8.585149043938145e-05</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-8.21269495645538e-05</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.53414793103002e-07</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.0531995940255e-05</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.469178773229942e-05</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.591384716448374e-05</v>
+      </c>
+      <c r="U3" t="n">
         <v>-0.0002688269887585193</v>
       </c>
-      <c r="J3" t="n">
+      <c r="V3" t="n">
         <v>-1.788413101166952e-05</v>
       </c>
-      <c r="K3" t="n">
+      <c r="W3" t="n">
+        <v>-9.927329665515572e-05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.0001195088698295876</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.340151629847242e-05</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.0001598354574525729</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.000297755264909938</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.493813670094823e-05</v>
+      </c>
+      <c r="AC3" t="n">
         <v>0.0001472437579650432</v>
       </c>
-      <c r="L3" t="n">
+      <c r="AD3" t="n">
         <v>6.555616778314288e-07</v>
       </c>
-      <c r="M3" t="n">
+      <c r="AE3" t="n">
+        <v>0.0001458133920095861</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0001758100115694106</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0002483989810571074</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>7.599655509693548e-05</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.0001439349580323324</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4.416381784722034e-07</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.0006162791978567839</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AL3" t="n">
         <v>4.51962259830907e-05</v>
       </c>
-      <c r="O3" t="n">
+      <c r="AM3" t="n">
+        <v>0.0003698368964251131</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.0004150508611928672</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.0003801028069574386</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.0001707047194940969</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.0006336396909318864</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.353929762146436e-05</v>
+      </c>
+      <c r="AS3" t="n">
         <v>-0.0006133402930572629</v>
       </c>
-      <c r="P3" t="n">
+      <c r="AT3" t="n">
         <v>-2.134761234628968e-05</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AU3" t="n">
+        <v>-0.0002862701949197799</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.0002883950946852565</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.0003764725406654179</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.0001529933360870928</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.0006281866226345301</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-1.754912409523968e-05</v>
+      </c>
+      <c r="BA3" t="n">
         <v>-5.550032437895425e-05</v>
       </c>
-      <c r="R3" t="n">
+      <c r="BB3" t="n">
         <v>-3.054762419196777e-05</v>
       </c>
-      <c r="S3" t="n">
+      <c r="BC3" t="n">
+        <v>5.899381721974351e-05</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.0001539351505925879</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-4.926877591060475e-05</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-5.095614324091002e-05</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-7.683218427700922e-05</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-3.052127794944681e-05</v>
+      </c>
+      <c r="BI3" t="n">
         <v>-2.30967634706758e-05</v>
       </c>
-      <c r="T3" t="n">
+      <c r="BJ3" t="n">
         <v>-2.556992330937646e-05</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.0002266019437229261</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-0.0002557332045398653</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-1.786489156074822e-05</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-5.600546137429774e-05</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-3.126667070318945e-05</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-2.561542714829557e-05</v>
       </c>
     </row>
     <row r="4">
@@ -668,46 +1196,190 @@
         <v>2.316736572538503e-05</v>
       </c>
       <c r="G4" t="n">
+        <v>0.0001982091343961656</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0002297793253092095</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0002510848280508071</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0001792908151401207</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000333018513629213</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.192386818933301e-05</v>
+      </c>
+      <c r="M4" t="n">
         <v>2.606838461360894e-05</v>
       </c>
-      <c r="H4" t="n">
+      <c r="N4" t="n">
         <v>-1.454420180380112e-05</v>
       </c>
-      <c r="I4" t="n">
+      <c r="O4" t="n">
+        <v>8.683263877173886e-05</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-8.316765888594091e-05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.838834234353271e-07</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.049732509272872e-05</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.418491905904375e-05</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.595568210177589e-05</v>
+      </c>
+      <c r="U4" t="n">
         <v>-0.0002735780144575983</v>
       </c>
-      <c r="J4" t="n">
+      <c r="V4" t="n">
         <v>-1.802077167667449e-05</v>
       </c>
-      <c r="K4" t="n">
+      <c r="W4" t="n">
+        <v>-0.0001011114145512693</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.0001216636810568161</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.304416400671471e-05</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.000162442636792548</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.0003031335945706815</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-1.502897248428781e-05</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0.0001372719125356525</v>
       </c>
-      <c r="L4" t="n">
+      <c r="AD4" t="n">
         <v>6.669405934189854e-07</v>
       </c>
-      <c r="M4" t="n">
+      <c r="AE4" t="n">
+        <v>0.0001467086840420961</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0001762941537890583</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0002507455938030034</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7.514913886552677e-05</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0001335767301497981</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4.496558005939733e-07</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.0006246671546250582</v>
       </c>
-      <c r="N4" t="n">
+      <c r="AL4" t="n">
         <v>4.622594860848039e-05</v>
       </c>
-      <c r="O4" t="n">
+      <c r="AM4" t="n">
+        <v>0.0003766038862522691</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.0004220121772959828</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.0003875024558510631</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.0001731859229039401</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.000643257808405906</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.450072447070852e-05</v>
+      </c>
+      <c r="AS4" t="n">
         <v>-0.0006220867508091033</v>
       </c>
-      <c r="P4" t="n">
+      <c r="AT4" t="n">
         <v>-2.205547025369015e-05</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="AU4" t="n">
+        <v>-0.0002915980294346809</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.000293726974632591</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.0003839612472802401</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.000156219961354509</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.0006380049744620919</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-1.812616756069474e-05</v>
+      </c>
+      <c r="BA4" t="n">
         <v>-5.161755325389095e-05</v>
       </c>
-      <c r="R4" t="n">
+      <c r="BB4" t="n">
         <v>-3.119385655736551e-05</v>
       </c>
-      <c r="S4" t="n">
+      <c r="BC4" t="n">
+        <v>6.209285493241623e-05</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.0001554242189740762</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-4.851031189900823e-05</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-5.029360909247771e-05</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-7.563027611467987e-05</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-3.116602238151245e-05</v>
+      </c>
+      <c r="BI4" t="n">
         <v>-2.35103361774236e-05</v>
       </c>
-      <c r="T4" t="n">
+      <c r="BJ4" t="n">
         <v>-2.602572021714877e-05</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.0002300989872310311</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0.0002601192682050169</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-1.945928488567006e-05</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-5.531041824724525e-05</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-3.178546467097476e-05</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-2.608516297186725e-05</v>
       </c>
     </row>
     <row r="5">
@@ -732,46 +1404,190 @@
         <v>2.330694587726612e-05</v>
       </c>
       <c r="G5" t="n">
+        <v>0.0002000958775170147</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.000231596888625063</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.000253825361141935</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0001800768804969266</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0003435979888308793</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.205287637480069e-05</v>
+      </c>
+      <c r="M5" t="n">
         <v>2.585319452919066e-05</v>
       </c>
-      <c r="H5" t="n">
+      <c r="N5" t="n">
         <v>-1.459414761484368e-05</v>
       </c>
-      <c r="I5" t="n">
+      <c r="O5" t="n">
+        <v>8.648492803331465e-05</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-8.283413626486436e-05</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-2.190287418102344e-08</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.044985856424319e-05</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.317817390779965e-05</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.603414602868725e-05</v>
+      </c>
+      <c r="U5" t="n">
         <v>-0.0002784615790005773</v>
       </c>
-      <c r="J5" t="n">
+      <c r="V5" t="n">
         <v>-1.815931318560615e-05</v>
       </c>
-      <c r="K5" t="n">
+      <c r="W5" t="n">
+        <v>-0.0001028203987516463</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.0001236302632605657</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.148056071542669e-05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.0001634102809475735</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.0003082157927565277</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-1.513355073257117e-05</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0.0001514191390015185</v>
       </c>
-      <c r="L5" t="n">
+      <c r="AD5" t="n">
         <v>6.811422963437508e-07</v>
       </c>
-      <c r="M5" t="n">
+      <c r="AE5" t="n">
+        <v>0.0001482790685258806</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0001774575503077358</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0002535655803512782</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>7.493705925298855e-05</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.000148195176734589</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>4.595212033109419e-07</v>
+      </c>
+      <c r="AK5" t="n">
         <v>0.0006353408098220825</v>
       </c>
-      <c r="N5" t="n">
+      <c r="AL5" t="n">
         <v>4.707209882326424e-05</v>
       </c>
-      <c r="O5" t="n">
+      <c r="AM5" t="n">
+        <v>0.0003829778870567679</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.0004286130133550614</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.0003944671771023422</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.0001755150296958163</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.0006524104974232614</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.531538070295937e-05</v>
+      </c>
+      <c r="AS5" t="n">
         <v>-0.0006327242008410394</v>
       </c>
-      <c r="P5" t="n">
+      <c r="AT5" t="n">
         <v>-2.248060445708688e-05</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="AU5" t="n">
+        <v>-0.0002966662868857384</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.000298762577585876</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.000390998407965526</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.0001591901964275166</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.0006475835107266903</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-1.846914528869092e-05</v>
+      </c>
+      <c r="BA5" t="n">
         <v>-5.240902464720421e-05</v>
       </c>
-      <c r="R5" t="n">
+      <c r="BB5" t="n">
         <v>-3.182601358275861e-05</v>
       </c>
-      <c r="S5" t="n">
+      <c r="BC5" t="n">
+        <v>6.45267718937248e-05</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.0001567229337524623</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-4.781296593137085e-05</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-4.964511026628315e-05</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-7.233675569295883e-05</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-3.179728810209781e-05</v>
+      </c>
+      <c r="BI5" t="n">
         <v>-2.390220834058709e-05</v>
       </c>
-      <c r="T5" t="n">
+      <c r="BJ5" t="n">
         <v>-2.641041101014707e-05</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.0002334469463676214</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.00026436333428137</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-2.094082810799591e-05</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-5.476650039781816e-05</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-3.228738569305278e-05</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-2.648220106493682e-05</v>
       </c>
     </row>
     <row r="6">
@@ -796,46 +1612,190 @@
         <v>2.35592251556227e-05</v>
       </c>
       <c r="G6" t="n">
+        <v>0.0002025935827987269</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0002339536877116188</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0002567267220001668</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0001809829554986209</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0003721561224665493</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.232800216006581e-05</v>
+      </c>
+      <c r="M6" t="n">
         <v>2.671727452252526e-05</v>
       </c>
-      <c r="H6" t="n">
+      <c r="N6" t="n">
         <v>-1.481695380789461e-05</v>
       </c>
-      <c r="I6" t="n">
+      <c r="O6" t="n">
+        <v>8.605365292169154e-05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-8.307179086841643e-05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-5.202766146794602e-07</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.875589057628531e-06</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.086222204728983e-05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.626357516215649e-05</v>
+      </c>
+      <c r="U6" t="n">
         <v>-0.0002783131785690784</v>
       </c>
-      <c r="J6" t="n">
+      <c r="V6" t="n">
         <v>-1.830335349950474e-05</v>
       </c>
-      <c r="K6" t="n">
+      <c r="W6" t="n">
+        <v>-0.0001024713928927667</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.0001231812202604488</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.160574811365223e-05</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.0001627424353500828</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.0003070532984565943</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1.529104156361427e-05</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.000209631456527859</v>
       </c>
-      <c r="L6" t="n">
+      <c r="AD6" t="n">
         <v>6.944321171431511e-07</v>
       </c>
-      <c r="M6" t="n">
+      <c r="AE6" t="n">
+        <v>0.0001521135855000466</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0001807202061172575</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0002564637397881597</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7.85633601481095e-05</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0002080047124763951</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4.688832291321887e-07</v>
+      </c>
+      <c r="AK6" t="n">
         <v>0.0006386750028468668</v>
       </c>
-      <c r="N6" t="n">
+      <c r="AL6" t="n">
         <v>4.673865987570025e-05</v>
       </c>
-      <c r="O6" t="n">
+      <c r="AM6" t="n">
+        <v>0.0003798544348683208</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.0004225825250614434</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.0003813888761214912</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.0001844917278503999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.0006505069322884083</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.507975245360285e-05</v>
+      </c>
+      <c r="AS6" t="n">
         <v>-0.0006354995421133935</v>
       </c>
-      <c r="P6" t="n">
+      <c r="AT6" t="n">
         <v>-2.177539317926858e-05</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AU6" t="n">
+        <v>-0.0002954172960016876</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.0002975017996504903</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.0003778410027734935</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.0001696335821179673</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.0006463085883297026</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-1.787348264770117e-05</v>
+      </c>
+      <c r="BA6" t="n">
         <v>-5.898973176954314e-05</v>
       </c>
-      <c r="R6" t="n">
+      <c r="BB6" t="n">
         <v>-3.197407932020724e-05</v>
       </c>
-      <c r="S6" t="n">
+      <c r="BC6" t="n">
+        <v>5.257719021756202e-05</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.0001435451267752796</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-4.712986628874205e-05</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-4.846332012675703e-05</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-6.638577906414866e-05</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-3.194699820596725e-05</v>
+      </c>
+      <c r="BI6" t="n">
         <v>-2.379711986577604e-05</v>
       </c>
-      <c r="T6" t="n">
+      <c r="BJ6" t="n">
         <v>-2.622961437737104e-05</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.0002329241542611271</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.0002635592245496809</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-2.173530810978264e-05</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-5.397179847932421e-05</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-3.220895086997189e-05</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-2.630802191561088e-05</v>
       </c>
     </row>
     <row r="7">
@@ -860,46 +1820,190 @@
         <v>2.386151390965097e-05</v>
       </c>
       <c r="G7" t="n">
+        <v>0.000205336618819274</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0002363204257562757</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0002578727144282311</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0001852702698670328</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0003638481430243701</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.263047827000264e-05</v>
+      </c>
+      <c r="M7" t="n">
         <v>2.435076203255448e-05</v>
       </c>
-      <c r="H7" t="n">
+      <c r="N7" t="n">
         <v>-1.513432926003588e-05</v>
       </c>
-      <c r="I7" t="n">
+      <c r="O7" t="n">
+        <v>8.924509165808558e-05</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-8.833530591800809e-05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.351656919723609e-06</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8.507568054483272e-06</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.906800909840968e-05</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.6536750990781e-05</v>
+      </c>
+      <c r="U7" t="n">
         <v>-0.0002733009750954807</v>
       </c>
-      <c r="J7" t="n">
+      <c r="V7" t="n">
         <v>-1.843552308855578e-05</v>
       </c>
-      <c r="K7" t="n">
+      <c r="W7" t="n">
+        <v>-0.000100826240668539</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0001212613569805399</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.699086897133384e-05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.0001655986125115305</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.0003018389688804746</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.544236693007406e-05</v>
+      </c>
+      <c r="AC7" t="n">
         <v>0.0002034071803791448</v>
       </c>
-      <c r="L7" t="n">
+      <c r="AD7" t="n">
         <v>6.747918064320402e-07</v>
       </c>
-      <c r="M7" t="n">
+      <c r="AE7" t="n">
+        <v>0.0001550242304801941</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0001825921644922346</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0002573087986093014</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8.264255302492529e-05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0002010814641835168</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>4.557429917895206e-07</v>
+      </c>
+      <c r="AK7" t="n">
         <v>0.0006270631565712392</v>
       </c>
-      <c r="N7" t="n">
+      <c r="AL7" t="n">
         <v>4.539099609246477e-05</v>
       </c>
-      <c r="O7" t="n">
+      <c r="AM7" t="n">
+        <v>0.0003726074355654418</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.0004116019699722528</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.0003651902952697128</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.0001885718083940446</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.0006408724002540112</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.380728933028877e-05</v>
+      </c>
+      <c r="AS7" t="n">
         <v>-0.0006244283867999911</v>
       </c>
-      <c r="P7" t="n">
+      <c r="AT7" t="n">
         <v>-2.099650919262785e-05</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="AU7" t="n">
+        <v>-0.0002899501123465598</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0.0002921311242971569</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.0003616737958509475</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.0001749483053572476</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.0006366933230310678</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-1.723116474749986e-05</v>
+      </c>
+      <c r="BA7" t="n">
         <v>-5.251788024907e-05</v>
       </c>
-      <c r="R7" t="n">
+      <c r="BB7" t="n">
         <v>-3.099501191172749e-05</v>
       </c>
-      <c r="S7" t="n">
+      <c r="BC7" t="n">
+        <v>4.386774162412621e-05</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.0001308418577536941</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-4.55015069746878e-05</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-4.647348032449372e-05</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-6.590251723537222e-05</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-3.097143780905753e-05</v>
+      </c>
+      <c r="BI7" t="n">
         <v>-2.322233376617078e-05</v>
       </c>
-      <c r="T7" t="n">
+      <c r="BJ7" t="n">
         <v>-2.566706643847283e-05</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.0002298713661730289</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0.0002587585768196732</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-2.203703661507461e-05</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-5.284540020511486e-05</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-3.155842932756059e-05</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-2.574753671069629e-05</v>
       </c>
     </row>
     <row r="8">
@@ -924,46 +2028,190 @@
         <v>2.406931707810145e-05</v>
       </c>
       <c r="G8" t="n">
+        <v>0.0002074278454529122</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0002382702223258093</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0002590296498965472</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0001887913240352646</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.00035043855314143</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.280565968248993e-05</v>
+      </c>
+      <c r="M8" t="n">
         <v>2.217075052612927e-05</v>
       </c>
-      <c r="H8" t="n">
+      <c r="N8" t="n">
         <v>-1.532603891973849e-05</v>
       </c>
-      <c r="I8" t="n">
+      <c r="O8" t="n">
+        <v>9.157945169135928e-05</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-9.222284279530868e-05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.963314389286097e-06</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7.588223525090143e-06</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.8230973839527e-05</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.668762524786871e-05</v>
+      </c>
+      <c r="U8" t="n">
         <v>-0.000270891236141324</v>
       </c>
-      <c r="J8" t="n">
+      <c r="V8" t="n">
         <v>-1.854795846156776e-05</v>
       </c>
-      <c r="K8" t="n">
+      <c r="W8" t="n">
+        <v>-0.000100244658824522</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.00012054959370289</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.05229935090756e-05</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.0001684350718278438</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.0002996590337716043</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.553804213472176e-05</v>
+      </c>
+      <c r="AC8" t="n">
         <v>0.0001826451043598354</v>
       </c>
-      <c r="L8" t="n">
+      <c r="AD8" t="n">
         <v>6.463691306635155e-07</v>
       </c>
-      <c r="M8" t="n">
+      <c r="AE8" t="n">
+        <v>0.0001568136503919959</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0001836721057770774</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0002582079032436013</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>8.493651694152504e-05</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0001794844138203189</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>4.36524203450972e-07</v>
+      </c>
+      <c r="AK8" t="n">
         <v>0.0006199072231538594</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AL8" t="n">
         <v>4.468534825718962e-05</v>
       </c>
-      <c r="O8" t="n">
+      <c r="AM8" t="n">
+        <v>0.0003703221736941487</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.000408783060265705</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.0003647787671070546</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.000184035103302449</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.0006362344138324261</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.306148912291974e-05</v>
+      </c>
+      <c r="AS8" t="n">
         <v>-0.0006177317118272185</v>
       </c>
-      <c r="P8" t="n">
+      <c r="AT8" t="n">
         <v>-2.112430047418457e-05</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AU8" t="n">
+        <v>-0.000287597271380946</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.0002898273232858628</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.0003614162560552359</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.0001704923924989998</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.0006319589447230101</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-1.734700890665408e-05</v>
+      </c>
+      <c r="BA8" t="n">
         <v>-4.653949508792721e-05</v>
       </c>
-      <c r="R8" t="n">
+      <c r="BB8" t="n">
         <v>-3.008710700669326e-05</v>
       </c>
-      <c r="S8" t="n">
+      <c r="BC8" t="n">
+        <v>4.761216041515581e-05</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.0001317186688538641</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-4.421726043801755e-05</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-4.528187128016725e-05</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-6.668746937066317e-05</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-3.006483530043624e-05</v>
+      </c>
+      <c r="BI8" t="n">
         <v>-2.294685691595078e-05</v>
       </c>
-      <c r="T8" t="n">
+      <c r="BJ8" t="n">
         <v>-2.540295827202499e-05</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.0002283843496115878</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-0.0002564252645242959</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-2.206050157838035e-05</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-5.244820567895658e-05</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-3.122267298749648e-05</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-2.548487282183487e-05</v>
       </c>
     </row>
     <row r="9">
@@ -988,46 +2236,190 @@
         <v>2.419465818093158e-05</v>
       </c>
       <c r="G9" t="n">
+        <v>0.0002087815810227767</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0002401308593107387</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.000260708766290918</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001907492114696652</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0003461302549112588</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.289299482072238e-05</v>
+      </c>
+      <c r="M9" t="n">
         <v>2.289610529260244e-05</v>
       </c>
-      <c r="H9" t="n">
+      <c r="N9" t="n">
         <v>-1.538071046525147e-05</v>
       </c>
-      <c r="I9" t="n">
+      <c r="O9" t="n">
+        <v>9.286400018027052e-05</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-9.303646220359951e-05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.591875616213656e-06</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8.059359970502555e-06</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.988764026667923e-05</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.674059785727877e-05</v>
+      </c>
+      <c r="U9" t="n">
         <v>-0.0002729776315391064</v>
       </c>
-      <c r="J9" t="n">
+      <c r="V9" t="n">
         <v>-1.86658107850235e-05</v>
       </c>
-      <c r="K9" t="n">
+      <c r="W9" t="n">
+        <v>-0.0001011973145068623</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.0001216573145939037</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.085752021230292e-05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.0001704956812318414</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.0003021716838702559</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1.560956116009038e-05</v>
+      </c>
+      <c r="AC9" t="n">
         <v>0.000169693972566165</v>
       </c>
-      <c r="L9" t="n">
+      <c r="AD9" t="n">
         <v>6.346764394038473e-07</v>
       </c>
-      <c r="M9" t="n">
+      <c r="AE9" t="n">
+        <v>0.0001572422770550475</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0001849501131800935</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0002598682185634971</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>8.515593071933836e-05</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0001661480200709775</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>4.279948200291983e-07</v>
+      </c>
+      <c r="AK9" t="n">
         <v>0.0006230186554603279</v>
       </c>
-      <c r="N9" t="n">
+      <c r="AL9" t="n">
         <v>4.518117566476576e-05</v>
       </c>
-      <c r="O9" t="n">
+      <c r="AM9" t="n">
+        <v>0.0003737056395038962</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.0004141744575463235</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.000373521848814562</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0001812362461350858</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.0006407598848454654</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.345118213677779e-05</v>
+      </c>
+      <c r="AS9" t="n">
         <v>-0.0006207826663739979</v>
       </c>
-      <c r="P9" t="n">
+      <c r="AT9" t="n">
         <v>-2.191952262364794e-05</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AU9" t="n">
+        <v>-0.0002900462714023888</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.0002922565909102559</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.0003701431269291788</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.0001665588351897895</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.0006360902916640043</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-1.802146107365843e-05</v>
+      </c>
+      <c r="BA9" t="n">
         <v>-4.737245035357773e-05</v>
       </c>
-      <c r="R9" t="n">
+      <c r="BB9" t="n">
         <v>-3.004181053256616e-05</v>
       </c>
-      <c r="S9" t="n">
+      <c r="BC9" t="n">
+        <v>5.277793388813734e-05</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.0001395509170833975</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-4.552067548502237e-05</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-4.683607403421775e-05</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-7.051292777759954e-05</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-3.001769619004335e-05</v>
+      </c>
+      <c r="BI9" t="n">
         <v>-2.317228791071102e-05</v>
       </c>
-      <c r="T9" t="n">
+      <c r="BJ9" t="n">
         <v>-2.565858085290529e-05</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.0002296596358064562</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0.0002581706794444472</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-2.098806362482719e-05</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-5.395473999669775e-05</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-3.146870221826248e-05</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-2.573266647232231e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1052,46 +2444,190 @@
         <v>2.411754030617885e-05</v>
       </c>
       <c r="G10" t="n">
+        <v>0.0002074806252494454</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0002396796189714223</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0002599802683107555</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0001897947076940909</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003420811553951353</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.27997425099602e-05</v>
+      </c>
+      <c r="M10" t="n">
         <v>2.536306965339463e-05</v>
       </c>
-      <c r="H10" t="n">
+      <c r="N10" t="n">
         <v>-1.531580528535414e-05</v>
       </c>
-      <c r="I10" t="n">
+      <c r="O10" t="n">
+        <v>9.271536691812798e-05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-9.154183499049395e-05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-6.056972665646754e-07</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9.166202289634384e-06</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.309002204332501e-05</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.666558273427654e-05</v>
+      </c>
+      <c r="U10" t="n">
         <v>-0.0002734090958256274</v>
       </c>
-      <c r="J10" t="n">
+      <c r="V10" t="n">
         <v>-1.861974124039989e-05</v>
       </c>
-      <c r="K10" t="n">
+      <c r="W10" t="n">
+        <v>-0.0001013748478726484</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.0001218859833898023</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.992026227526367e-05</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.0001698810956440866</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.0003027938946615905</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-1.555349808768369e-05</v>
+      </c>
+      <c r="AC10" t="n">
         <v>0.0001593803171999753</v>
       </c>
-      <c r="L10" t="n">
+      <c r="AD10" t="n">
         <v>6.221791863936232e-07</v>
       </c>
-      <c r="M10" t="n">
+      <c r="AE10" t="n">
+        <v>0.0001554837945150211</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.0001849600521381944</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.0002592152741272002</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>8.41333603602834e-05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.0001556933711981401</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>4.187287458989886e-07</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0.0006239991053007543</v>
       </c>
-      <c r="N10" t="n">
+      <c r="AL10" t="n">
         <v>4.529326906776987e-05</v>
       </c>
-      <c r="O10" t="n">
+      <c r="AM10" t="n">
+        <v>0.0003748177841771394</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.000418246490880847</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.0003805849410127848</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.0001777599536580965</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.0006425305036827922</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.350292147137225e-05</v>
+      </c>
+      <c r="AS10" t="n">
         <v>-0.0006213401211425662</v>
       </c>
-      <c r="P10" t="n">
+      <c r="AT10" t="n">
         <v>-2.228319681307767e-05</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AU10" t="n">
+        <v>-0.0002907179587054998</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0.000292908021947369</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.0003770475159399211</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.0001608918537385762</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.0006371135823428631</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-1.83423726412002e-05</v>
+      </c>
+      <c r="BA10" t="n">
         <v>-5.261447950033471e-05</v>
       </c>
-      <c r="R10" t="n">
+      <c r="BB10" t="n">
         <v>-2.981055149575695e-05</v>
       </c>
-      <c r="S10" t="n">
+      <c r="BC10" t="n">
+        <v>5.624631739920005e-05</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.0001490142021793872</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-4.841674672206864e-05</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-4.995962808607146e-05</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-7.703401206526905e-05</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-2.978457087010611e-05</v>
+      </c>
+      <c r="BI10" t="n">
         <v>-2.33039609156549e-05</v>
       </c>
-      <c r="T10" t="n">
+      <c r="BJ10" t="n">
         <v>-2.581221633590758e-05</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.0002297994506079704</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0.0002587079361546785</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-1.832741327234544e-05</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-5.671376493410207e-05</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-3.158368053846061e-05</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-2.586389200587291e-05</v>
       </c>
     </row>
     <row r="11">
@@ -1116,46 +2652,190 @@
         <v>2.387292806815822e-05</v>
       </c>
       <c r="G11" t="n">
+        <v>0.0002029550378210843</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0002356506010983139</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0002552373334765434</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0001856739254435524</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.00033115383121185</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.257849519082811e-05</v>
+      </c>
+      <c r="M11" t="n">
         <v>2.69803076662356e-05</v>
       </c>
-      <c r="H11" t="n">
+      <c r="N11" t="n">
         <v>-1.523032460681861e-05</v>
       </c>
-      <c r="I11" t="n">
+      <c r="O11" t="n">
+        <v>9.064165351446718e-05</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-8.899748354451731e-05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.878884472096615e-08</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.605977538740262e-06</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.521615144563839e-05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.653276194701903e-05</v>
+      </c>
+      <c r="U11" t="n">
         <v>-0.0002666223444975913</v>
       </c>
-      <c r="J11" t="n">
+      <c r="V11" t="n">
         <v>-1.837371382862329e-05</v>
       </c>
-      <c r="K11" t="n">
+      <c r="W11" t="n">
+        <v>-9.884023165795952e-05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.0001189372342196293</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.954545041371603e-05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.00016544979007449</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.0002955158124677837</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-1.537183561595157e-05</v>
+      </c>
+      <c r="AC11" t="n">
         <v>0.0001489616115577519</v>
       </c>
-      <c r="L11" t="n">
+      <c r="AD11" t="n">
         <v>6.004136707815633e-07</v>
       </c>
-      <c r="M11" t="n">
+      <c r="AE11" t="n">
+        <v>0.0001523333339719102</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.000182933290489018</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.0002544878516346216</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>8.37191691971384e-05</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.0001452345895813778</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4.035746599129197e-07</v>
+      </c>
+      <c r="AK11" t="n">
         <v>0.0006108880625106394</v>
       </c>
-      <c r="N11" t="n">
+      <c r="AL11" t="n">
         <v>4.386612272355705e-05</v>
       </c>
-      <c r="O11" t="n">
+      <c r="AM11" t="n">
+        <v>0.0003667942655738443</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.0004122151876799762</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.00037845250335522</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.0001680549030425027</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.0006297166692093015</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.214629007037729e-05</v>
+      </c>
+      <c r="AS11" t="n">
         <v>-0.0006078102742321789</v>
       </c>
-      <c r="P11" t="n">
+      <c r="AT11" t="n">
         <v>-2.14290357689606e-05</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="AU11" t="n">
+        <v>-0.0002835345221683383</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.0002857065410353243</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0.0003747908631339669</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.000148743114550598</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.0006235788459889591</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-1.765032902767416e-05</v>
+      </c>
+      <c r="BA11" t="n">
         <v>-5.685599899152294e-05</v>
       </c>
-      <c r="R11" t="n">
+      <c r="BB11" t="n">
         <v>-2.876240978366695e-05</v>
       </c>
-      <c r="S11" t="n">
+      <c r="BC11" t="n">
+        <v>5.941623385297135e-05</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.0001560880045872182</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-5.025209247833118e-05</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-5.197109931032173e-05</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-8.208947838284075e-05</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-2.873790072044358e-05</v>
+      </c>
+      <c r="BI11" t="n">
         <v>-2.276622581121046e-05</v>
       </c>
-      <c r="T11" t="n">
+      <c r="BJ11" t="n">
         <v>-2.525384843465872e-05</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.0002249797980766743</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0.0002528431359678507</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-1.525871084595565e-05</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-5.845462146680802e-05</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-3.088478479185142e-05</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-2.527664582885336e-05</v>
       </c>
     </row>
     <row r="12">
@@ -1180,46 +2860,190 @@
         <v>2.363120438531041e-05</v>
       </c>
       <c r="G12" t="n">
+        <v>0.0001976183702936396</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0002304107183590531</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0002492501516826451</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0001807020016713068</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0003176295722369105</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.238425622635987e-05</v>
+      </c>
+      <c r="M12" t="n">
         <v>2.761649739113636e-05</v>
       </c>
-      <c r="H12" t="n">
+      <c r="N12" t="n">
         <v>-1.515968870080542e-05</v>
       </c>
-      <c r="I12" t="n">
+      <c r="O12" t="n">
+        <v>8.787371189100668e-05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-8.616040577180684e-05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.735774155051331e-07</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9.636298273107968e-06</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.621524592745118e-05</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.642602182982955e-05</v>
+      </c>
+      <c r="U12" t="n">
         <v>-0.0002571756194811314</v>
       </c>
-      <c r="J12" t="n">
+      <c r="V12" t="n">
         <v>-1.811812398955226e-05</v>
       </c>
-      <c r="K12" t="n">
+      <c r="W12" t="n">
+        <v>-9.536333527648821e-05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.0001148701048805378</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.933951534738299e-05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.000159805582370609</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.0002853187033906579</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.520137720945058e-05</v>
+      </c>
+      <c r="AC12" t="n">
         <v>0.0001385576761094853</v>
       </c>
-      <c r="L12" t="n">
+      <c r="AD12" t="n">
         <v>5.926762014496489e-07</v>
       </c>
-      <c r="M12" t="n">
+      <c r="AE12" t="n">
+        <v>0.0001491209695814177</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.0001801952894311398</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.0002484982833266258</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>8.380053623113781e-05</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.0001347970392089337</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3.985003047546343e-07</v>
+      </c>
+      <c r="AK12" t="n">
         <v>0.0005921449046581984</v>
       </c>
-      <c r="N12" t="n">
+      <c r="AL12" t="n">
         <v>4.224250005790964e-05</v>
       </c>
-      <c r="O12" t="n">
+      <c r="AM12" t="n">
+        <v>0.0003554273280315101</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.0004022250068373978</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.0003722457913681865</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.0001562616671435535</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.0006111317779868841</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.066041219630279e-05</v>
+      </c>
+      <c r="AS12" t="n">
         <v>-0.0005888179293833673</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AT12" t="n">
         <v>-2.009773925237823e-05</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AU12" t="n">
+        <v>-0.0002733999281190336</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.0002755514578893781</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-0.0003685036208480597</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.0001348455989500508</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.0006045019836165011</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-1.654805782891344e-05</v>
+      </c>
+      <c r="BA12" t="n">
         <v>-5.869101369171403e-05</v>
       </c>
-      <c r="R12" t="n">
+      <c r="BB12" t="n">
         <v>-2.796767330437433e-05</v>
       </c>
-      <c r="S12" t="n">
+      <c r="BC12" t="n">
+        <v>6.251860031625256e-05</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.0001609082537470385</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-5.099812551634386e-05</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-5.286026134854183e-05</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-8.464411803288385e-05</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-2.794501597236376e-05</v>
+      </c>
+      <c r="BI12" t="n">
         <v>-2.201042843807954e-05</v>
       </c>
-      <c r="T12" t="n">
+      <c r="BJ12" t="n">
         <v>-2.446055623295251e-05</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.000218340297578834</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0.0002448773011565208</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-1.30842245198437e-05</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-5.865294224349782e-05</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-2.991330802615266e-05</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-2.446440339554101e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1244,46 +3068,190 @@
         <v>2.353646232222673e-05</v>
       </c>
       <c r="G13" t="n">
+        <v>0.0001959379005711526</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0002285808295710012</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0002477122761774808</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0001787534129107371</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0003144584479741752</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.230856443929952e-05</v>
+      </c>
+      <c r="M13" t="n">
         <v>2.756969479378313e-05</v>
       </c>
-      <c r="H13" t="n">
+      <c r="N13" t="n">
         <v>-1.504705141996965e-05</v>
       </c>
-      <c r="I13" t="n">
+      <c r="O13" t="n">
+        <v>8.655517012812197e-05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-8.421272650593892e-05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6.44962483420386e-07</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9.946182217390742e-06</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.641633156803437e-05</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.634921500226483e-05</v>
+      </c>
+      <c r="U13" t="n">
         <v>-0.0002571722434367985</v>
       </c>
-      <c r="J13" t="n">
+      <c r="V13" t="n">
         <v>-1.808785418688785e-05</v>
       </c>
-      <c r="K13" t="n">
+      <c r="W13" t="n">
+        <v>-9.538204176351428e-05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.0001149268937297165</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.764748594723642e-05</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.0001583497505635023</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.0002853881742339581</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.517242617410375e-05</v>
+      </c>
+      <c r="AC13" t="n">
         <v>0.0001307821075897664</v>
       </c>
-      <c r="L13" t="n">
+      <c r="AD13" t="n">
         <v>6.170762958390696e-07</v>
       </c>
-      <c r="M13" t="n">
+      <c r="AE13" t="n">
+        <v>0.0001476554461987689</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.0001787434448488057</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.0002470820036251098</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8.233598782680929e-05</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.000126931321574375</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4.155490387347527e-07</v>
+      </c>
+      <c r="AK13" t="n">
         <v>0.0005916038062423468</v>
       </c>
-      <c r="N13" t="n">
+      <c r="AL13" t="n">
         <v>4.28541170549579e-05</v>
       </c>
-      <c r="O13" t="n">
+      <c r="AM13" t="n">
+        <v>0.0003560868790373206</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.0004039240593556315</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.0003755598736461252</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.0001533646427560598</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.0006109075038693845</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.128844011574984e-05</v>
+      </c>
+      <c r="AS13" t="n">
         <v>-0.0005883867270313203</v>
       </c>
-      <c r="P13" t="n">
+      <c r="AT13" t="n">
         <v>-2.011728793149814e-05</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="AU13" t="n">
+        <v>-0.0002734824374783784</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.0002756153116934001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.0003718284133356065</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.000131798122311011</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.0006043732282705605</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-1.65472665685229e-05</v>
+      </c>
+      <c r="BA13" t="n">
         <v>-5.750090713263489e-05</v>
       </c>
-      <c r="R13" t="n">
+      <c r="BB13" t="n">
         <v>-2.876937469409313e-05</v>
       </c>
-      <c r="S13" t="n">
+      <c r="BC13" t="n">
+        <v>6.5803193137981e-05</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.0001642568677198142</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-5.096543100080453e-05</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-5.295324808685109e-05</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-8.39031272334978e-05</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-2.874536949093454e-05</v>
+      </c>
+      <c r="BI13" t="n">
         <v>-2.213039806520101e-05</v>
       </c>
-      <c r="T13" t="n">
+      <c r="BJ13" t="n">
         <v>-2.457830305502284e-05</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.0002183464093832299</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0.000245378352701664</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-1.383399740007007e-05</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-5.784392851637676e-05</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-3.002050652867183e-05</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-2.458916605974082e-05</v>
       </c>
     </row>
     <row r="14">
@@ -1308,46 +3276,190 @@
         <v>2.355231481487863e-05</v>
       </c>
       <c r="G14" t="n">
+        <v>0.0001975888881133869</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0002299575280630961</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0002502890420146286</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.000179495764314197</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0003209896385669708</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.231005237263162e-05</v>
+      </c>
+      <c r="M14" t="n">
         <v>2.69719457719475e-05</v>
       </c>
-      <c r="H14" t="n">
+      <c r="N14" t="n">
         <v>-1.491466264269548e-05</v>
       </c>
-      <c r="I14" t="n">
+      <c r="O14" t="n">
+        <v>8.66234113345854e-05</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-8.339673513546586e-05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.708704975404544e-07</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.041630457621068e-05</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.597408795030788e-05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.629143480386119e-05</v>
+      </c>
+      <c r="U14" t="n">
         <v>-0.0002657501609064639</v>
       </c>
-      <c r="J14" t="n">
+      <c r="V14" t="n">
         <v>-1.821641671995167e-05</v>
       </c>
-      <c r="K14" t="n">
+      <c r="W14" t="n">
+        <v>-9.85199076239951e-05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.0001186103036161512</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.492573574068956e-05</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.0001606210571480915</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.0002948038745671511</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.523593346064445e-05</v>
+      </c>
+      <c r="AC14" t="n">
         <v>0.0001257588446605951</v>
       </c>
-      <c r="L14" t="n">
+      <c r="AD14" t="n">
         <v>6.53117865567765e-07</v>
       </c>
-      <c r="M14" t="n">
+      <c r="AE14" t="n">
+        <v>0.0001477551413699985</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0001784854248398915</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0002498429676052183</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>7.944244862301275e-05</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0001217821700265631</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>4.402490105803736e-07</v>
+      </c>
+      <c r="AK14" t="n">
         <v>0.0006080844323150814</v>
       </c>
-      <c r="N14" t="n">
+      <c r="AL14" t="n">
         <v>4.499866918195039e-05</v>
       </c>
-      <c r="O14" t="n">
+      <c r="AM14" t="n">
+        <v>0.0003677728236652911</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.0004162168188486248</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0003878830757457763</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0001584627025295049</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.0006277887150645256</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.3336895032553e-05</v>
+      </c>
+      <c r="AS14" t="n">
         <v>-0.000605215725954622</v>
       </c>
-      <c r="P14" t="n">
+      <c r="AT14" t="n">
         <v>-2.128227970388252e-05</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="AU14" t="n">
+        <v>-0.0002829323930200189</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.00028505056980066</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.0003842517326120287</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.0001383941125823185</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.0006217681220732629</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-1.74937831616262e-05</v>
+      </c>
+      <c r="BA14" t="n">
         <v>-5.435986531665549e-05</v>
       </c>
-      <c r="R14" t="n">
+      <c r="BB14" t="n">
         <v>-3.042669959540945e-05</v>
       </c>
-      <c r="S14" t="n">
+      <c r="BC14" t="n">
+        <v>6.945764471311122e-05</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.0001666566095082089</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-5.030478496337309e-05</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-5.240637256065384e-05</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-8.100626291707158e-05</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-3.039952753169928e-05</v>
+      </c>
+      <c r="BI14" t="n">
         <v>-2.292605313414242e-05</v>
       </c>
-      <c r="T14" t="n">
+      <c r="BJ14" t="n">
         <v>-2.541969479352701e-05</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.0002244587522000074</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-0.0002533933438826352</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-1.653272192925215e-05</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-5.666632205247879e-05</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-3.100112735410221e-05</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-2.545432471379172e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1372,46 +3484,190 @@
         <v>2.360305916226935e-05</v>
       </c>
       <c r="G15" t="n">
+        <v>0.0001991536992136389</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0002313200675416738</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0002530291385482997</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0001794242998585105</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0003349434409756213</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.23591887333896e-05</v>
+      </c>
+      <c r="M15" t="n">
         <v>2.696741830732208e-05</v>
       </c>
-      <c r="H15" t="n">
+      <c r="N15" t="n">
         <v>-1.485749817220494e-05</v>
       </c>
-      <c r="I15" t="n">
+      <c r="O15" t="n">
+        <v>8.577911648899317e-05</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-8.197013812605292e-05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.792329152929597e-07</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.06697352748597e-05</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.492493851808831e-05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-1.629150028747972e-05</v>
+      </c>
+      <c r="U15" t="n">
         <v>-0.0002731770800892264</v>
       </c>
-      <c r="J15" t="n">
+      <c r="V15" t="n">
         <v>-1.83273441507481e-05</v>
       </c>
-      <c r="K15" t="n">
+      <c r="W15" t="n">
+        <v>-0.000101069497759454</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.0001215656084241346</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.195679669763194e-05</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.0001613979984540492</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.0003025887417607009</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-1.53071123349946e-05</v>
+      </c>
+      <c r="AC15" t="n">
         <v>0.000142687073093839</v>
       </c>
-      <c r="L15" t="n">
+      <c r="AD15" t="n">
         <v>6.837834689576994e-07</v>
       </c>
-      <c r="M15" t="n">
+      <c r="AE15" t="n">
+        <v>0.0001486240071244538</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.0001789180678315461</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0002527461911085993</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>7.765257032588124e-05</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0001393104757880792</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>4.611561905676353e-07</v>
+      </c>
+      <c r="AK15" t="n">
         <v>0.000624222622718662</v>
       </c>
-      <c r="N15" t="n">
+      <c r="AL15" t="n">
         <v>4.650565824704245e-05</v>
       </c>
-      <c r="O15" t="n">
+      <c r="AM15" t="n">
+        <v>0.0003772107884287834</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.0004256994288880378</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.0003965680371038616</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.0001639470137888566</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.0006419438868761063</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.480762436287478e-05</v>
+      </c>
+      <c r="AS15" t="n">
         <v>-0.0006213314482010901</v>
       </c>
-      <c r="P15" t="n">
+      <c r="AT15" t="n">
         <v>-2.190636223531328e-05</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="AU15" t="n">
+        <v>-0.0002907807356677949</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.0002928561007138342</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.0003930063976440579</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.0001452610013075173</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.0006365725421346724</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-1.799637357180472e-05</v>
+      </c>
+      <c r="BA15" t="n">
         <v>-5.51964076294098e-05</v>
       </c>
-      <c r="R15" t="n">
+      <c r="BB15" t="n">
         <v>-3.169644332956523e-05</v>
       </c>
-      <c r="S15" t="n">
+      <c r="BC15" t="n">
+        <v>7.079516217345372e-05</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.0001668314507696778</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-4.958020508638583e-05</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-5.169498399482109e-05</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-7.6527867349796e-05</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-3.166758324368857e-05</v>
+      </c>
+      <c r="BI15" t="n">
         <v>-2.354669959458988e-05</v>
       </c>
-      <c r="T15" t="n">
+      <c r="BJ15" t="n">
         <v>-2.60427132161567e-05</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.0002296139864483848</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0.0002600433945190161</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-1.88148351298878e-05</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-5.57269413548056e-05</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-3.17931808240246e-05</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-2.60963206528686e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1436,46 +3692,190 @@
         <v>2.377064083702862e-05</v>
       </c>
       <c r="G16" t="n">
+        <v>0.0002014416677411646</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0002333482843823731</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0002558446431066841</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0001798671873984858</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0003651754814200103</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.255583603982814e-05</v>
+      </c>
+      <c r="M16" t="n">
         <v>2.787648554658517e-05</v>
       </c>
-      <c r="H16" t="n">
+      <c r="N16" t="n">
         <v>-1.499258269177517e-05</v>
       </c>
-      <c r="I16" t="n">
+      <c r="O16" t="n">
+        <v>8.513103239238262e-05</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-8.164157043211162e-05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-6.78384921570796e-08</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.026240624923958e-05</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.249636210966855e-05</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.644988151383586e-05</v>
+      </c>
+      <c r="U16" t="n">
         <v>-0.000274764170171693</v>
       </c>
-      <c r="J16" t="n">
+      <c r="V16" t="n">
         <v>-1.843275276769418e-05</v>
       </c>
-      <c r="K16" t="n">
+      <c r="W16" t="n">
+        <v>-0.000101287048892118</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.0001217879253090359</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.128222538682166e-05</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.000160729352501221</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.000303279550280422</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1.542529207654297e-05</v>
+      </c>
+      <c r="AC16" t="n">
         <v>0.0002025096910074353</v>
       </c>
-      <c r="L16" t="n">
+      <c r="AD16" t="n">
         <v>7.067084766276821e-07</v>
       </c>
-      <c r="M16" t="n">
+      <c r="AE16" t="n">
+        <v>0.0001518959761597216</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.0001815317518776283</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.0002555957471486181</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>8.008098666323349e-05</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.0002007949951803312</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>4.769946144733694e-07</v>
+      </c>
+      <c r="AK16" t="n">
         <v>0.0006312812911346555</v>
       </c>
-      <c r="N16" t="n">
+      <c r="AL16" t="n">
         <v>4.657239696825854e-05</v>
       </c>
-      <c r="O16" t="n">
+      <c r="AM16" t="n">
+        <v>0.0003758901730179787</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.0004210356855764985</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.0003838810080196708</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.000175714012584649</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.0006434757960960269</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.496965630096383e-05</v>
+      </c>
+      <c r="AS16" t="n">
         <v>-0.0006278330693021417</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AT16" t="n">
         <v>-2.131196379195899e-05</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AU16" t="n">
+        <v>-0.000291453703539446</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0.0002935150114353746</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0.0003802333085332066</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.0001592311746207997</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.0006388939218595624</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-1.748909562593326e-05</v>
+      </c>
+      <c r="BA16" t="n">
         <v>-6.152306741569191e-05</v>
       </c>
-      <c r="R16" t="n">
+      <c r="BB16" t="n">
         <v>-3.221482984372415e-05</v>
       </c>
-      <c r="S16" t="n">
+      <c r="BC16" t="n">
+        <v>5.738509935326874e-05</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.0001519243523944169</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-4.877633909927681e-05</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-5.034022251493298e-05</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-6.969559035496786e-05</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-3.218722849851474e-05</v>
+      </c>
+      <c r="BI16" t="n">
         <v>-2.359286372666247e-05</v>
       </c>
-      <c r="T16" t="n">
+      <c r="BJ16" t="n">
         <v>-2.601909181976225e-05</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.0002303369110450149</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-0.0002608428185340017</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-2.020223109866492e-05</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-5.465079448185861e-05</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-3.190899587934837e-05</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-2.608416980365291e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1500,46 +3900,190 @@
         <v>2.399230106675532e-05</v>
       </c>
       <c r="G17" t="n">
+        <v>0.0002040185208898038</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0002354142925469205</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0002568526833783835</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0001838562602642924</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0003585178637877107</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.278084866702557e-05</v>
+      </c>
+      <c r="M17" t="n">
         <v>2.545739698689431e-05</v>
       </c>
-      <c r="H17" t="n">
+      <c r="N17" t="n">
         <v>-1.523535593150882e-05</v>
       </c>
-      <c r="I17" t="n">
+      <c r="O17" t="n">
+        <v>8.824170799925923e-05</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-8.664326014695689e-05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-8.913415854294726e-07</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.973443073045928e-06</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.054216358577833e-05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.665665513428394e-05</v>
+      </c>
+      <c r="U17" t="n">
         <v>-0.0002709557011257857</v>
       </c>
-      <c r="J17" t="n">
+      <c r="V17" t="n">
         <v>-1.852123932621907e-05</v>
       </c>
-      <c r="K17" t="n">
+      <c r="W17" t="n">
+        <v>-0.0001000322590698488</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.0001203329229610972</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.621483170310967e-05</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.0001636828383198008</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.0002993534435518086</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-1.553399306430947e-05</v>
+      </c>
+      <c r="AC17" t="n">
         <v>0.0001972881727851927</v>
       </c>
-      <c r="L17" t="n">
+      <c r="AD17" t="n">
         <v>6.914644359312661e-07</v>
       </c>
-      <c r="M17" t="n">
+      <c r="AE17" t="n">
+        <v>0.0001543713151477277</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.0001828464446589351</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.000256338797044009</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>8.324978989548981e-05</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.0001949096185853705</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>4.668309259159287e-07</v>
+      </c>
+      <c r="AK17" t="n">
         <v>0.0006221672520041466</v>
       </c>
-      <c r="N17" t="n">
+      <c r="AL17" t="n">
         <v>4.544853072729893e-05</v>
       </c>
-      <c r="O17" t="n">
+      <c r="AM17" t="n">
+        <v>0.0003699448134284467</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.0004108896537218243</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.0003676130436360836</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.0001821451442083344</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.0006362476269714534</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.391663242131472e-05</v>
+      </c>
+      <c r="AS17" t="n">
         <v>-0.0006193272420205176</v>
       </c>
-      <c r="P17" t="n">
+      <c r="AT17" t="n">
         <v>-2.061915438389406e-05</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="AU17" t="n">
+        <v>-0.0002873374614864588</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.0002894961216952652</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.0003639989881776273</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.0001673843653406948</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.0006317686638794839</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-1.691606303211302e-05</v>
+      </c>
+      <c r="BA17" t="n">
         <v>-5.46936244063545e-05</v>
       </c>
-      <c r="R17" t="n">
+      <c r="BB17" t="n">
         <v>-3.141778506687842e-05</v>
       </c>
-      <c r="S17" t="n">
+      <c r="BC17" t="n">
+        <v>4.740086660603993e-05</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.0001375359715893865</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-4.696385076385923e-05</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-4.811733015230857e-05</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-6.851368380011991e-05</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-3.13935088342987e-05</v>
+      </c>
+      <c r="BI17" t="n">
         <v>-2.311880052729975e-05</v>
       </c>
-      <c r="T17" t="n">
+      <c r="BJ17" t="n">
         <v>-2.556056278990582e-05</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.0002281436027260497</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.0002571111836005002</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-2.093999319185968e-05</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-5.332964065019041e-05</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-3.138895044685341e-05</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-2.563132511568256e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1564,46 +4108,190 @@
         <v>2.412591129541397e-05</v>
       </c>
       <c r="G18" t="n">
+        <v>0.0002059754624497145</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0002371087030041963</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0002578581334091723</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.0001871761778602377</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0003464176552370191</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.288282666995656e-05</v>
+      </c>
+      <c r="M18" t="n">
         <v>2.317797952855472e-05</v>
       </c>
-      <c r="H18" t="n">
+      <c r="N18" t="n">
         <v>-1.536359013698529e-05</v>
       </c>
-      <c r="I18" t="n">
+      <c r="O18" t="n">
+        <v>9.055215195985511e-05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-9.042967576533556e-05</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.519862962595653e-06</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.08029744803207e-06</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.952589784399606e-05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-1.674690247455146e-05</v>
+      </c>
+      <c r="U18" t="n">
         <v>-0.000269384850980714</v>
       </c>
-      <c r="J18" t="n">
+      <c r="V18" t="n">
         <v>-1.858974792412482e-05</v>
       </c>
-      <c r="K18" t="n">
+      <c r="W18" t="n">
+        <v>-9.972078987630084e-05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.0001199431790155359</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.949030411196873e-05</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.0001666436000959948</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.0002980714198201895</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1.558730218675919e-05</v>
+      </c>
+      <c r="AC18" t="n">
         <v>0.000177223002538085</v>
       </c>
-      <c r="L18" t="n">
+      <c r="AD18" t="n">
         <v>6.640389074163977e-07</v>
       </c>
-      <c r="M18" t="n">
+      <c r="AE18" t="n">
+        <v>0.0001558267103973776</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.0001834574795793742</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.0002571159857325256</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>8.485007856506854e-05</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.0001740311563480645</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>4.4831071477347e-07</v>
+      </c>
+      <c r="AK18" t="n">
         <v>0.0006167428800836205</v>
       </c>
-      <c r="N18" t="n">
+      <c r="AL18" t="n">
         <v>4.485175668378361e-05</v>
       </c>
-      <c r="O18" t="n">
+      <c r="AM18" t="n">
+        <v>0.0003686734999064356</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.0004087355046067387</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.000366984837455675</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.0001795113203115761</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.000633281480986625</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.327431815909222e-05</v>
+      </c>
+      <c r="AS18" t="n">
         <v>-0.0006144176586531103</v>
       </c>
-      <c r="P18" t="n">
+      <c r="AT18" t="n">
         <v>-2.082418541249353e-05</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="AU18" t="n">
+        <v>-0.0002859391388483346</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.0002881484979297966</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0.0003635348111856729</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.0001651010243222117</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.0006287703290581703</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-1.709491334622726e-05</v>
+      </c>
+      <c r="BA18" t="n">
         <v>-4.835181607631966e-05</v>
       </c>
-      <c r="R18" t="n">
+      <c r="BB18" t="n">
         <v>-3.057288631680422e-05</v>
       </c>
-      <c r="S18" t="n">
+      <c r="BC18" t="n">
+        <v>5.016026625526138e-05</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.000136966336867772</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-4.546918353298679e-05</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-4.667479151976295e-05</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-6.872884114272892e-05</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-3.054983972106129e-05</v>
+      </c>
+      <c r="BI18" t="n">
         <v>-2.290900556545239e-05</v>
       </c>
-      <c r="T18" t="n">
+      <c r="BJ18" t="n">
         <v>-2.536399188102223e-05</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.0002272507263114676</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.0002554904494900256</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-2.12804734474048e-05</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-5.279609104036354e-05</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-3.113966886303388e-05</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-2.543889968364965e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1628,46 +4316,190 @@
         <v>2.418694202788174e-05</v>
       </c>
       <c r="G19" t="n">
+        <v>0.000207233868422918</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0002387832646491006</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0002594099787529558</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0001890127896331251</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0003430366050451994</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.290537304361351e-05</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.378668068558909e-05</v>
       </c>
-      <c r="H19" t="n">
+      <c r="N19" t="n">
         <v>-1.536587660666555e-05</v>
       </c>
-      <c r="I19" t="n">
+      <c r="O19" t="n">
+        <v>9.184364171233028e-05</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-9.123352356255054e-05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.176999603558215e-06</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8.547675861336756e-06</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.100651520071551e-05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.674731356615666e-05</v>
+      </c>
+      <c r="U19" t="n">
         <v>-0.0002720545162446797</v>
       </c>
-      <c r="J19" t="n">
+      <c r="V19" t="n">
         <v>-1.866744969447609e-05</v>
       </c>
-      <c r="K19" t="n">
+      <c r="W19" t="n">
+        <v>-0.0001008597246254794</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.0001212726347148418</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.968982905964367e-05</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.0001688320626271889</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.000301208405289799</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.562020224810112e-05</v>
+      </c>
+      <c r="AC19" t="n">
         <v>0.0001647662575123832</v>
       </c>
-      <c r="L19" t="n">
+      <c r="AD19" t="n">
         <v>6.514451911243668e-07</v>
       </c>
-      <c r="M19" t="n">
+      <c r="AE19" t="n">
+        <v>0.0001560062228236347</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.0001843551872298121</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.0002586589835118502</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>8.454884664388373e-05</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.0001612023334018886</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4.3920132952735e-07</v>
+      </c>
+      <c r="AK19" t="n">
         <v>0.0006210686406120658</v>
       </c>
-      <c r="N19" t="n">
+      <c r="AL19" t="n">
         <v>4.539427027339116e-05</v>
       </c>
-      <c r="O19" t="n">
+      <c r="AM19" t="n">
+        <v>0.0003727575240191072</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.000414565991377458</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.0003754730860237032</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.0001781744649633765</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.0006389684276655316</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.370411988929845e-05</v>
+      </c>
+      <c r="AS19" t="n">
         <v>-0.0006187107064761221</v>
       </c>
-      <c r="P19" t="n">
+      <c r="AT19" t="n">
         <v>-2.168898390664253e-05</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="AU19" t="n">
+        <v>-0.0002890607574954629</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-0.0002912522468250245</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.0003720136010088027</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.0001628037862246856</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.0006341091357171535</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-1.7826716430136e-05</v>
+      </c>
+      <c r="BA19" t="n">
         <v>-4.884841837338172e-05</v>
       </c>
-      <c r="R19" t="n">
+      <c r="BB19" t="n">
         <v>-3.052334432140924e-05</v>
       </c>
-      <c r="S19" t="n">
+      <c r="BC19" t="n">
+        <v>5.458700616145507e-05</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.0001436076563550159</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-4.656443707062863e-05</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-4.798850568477064e-05</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-7.20949683454819e-05</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-3.04984423564747e-05</v>
+      </c>
+      <c r="BI19" t="n">
         <v>-2.317610596946906e-05</v>
       </c>
-      <c r="T19" t="n">
+      <c r="BJ19" t="n">
         <v>-2.566228795330971e-05</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.000228937336942181</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-0.000257709005381912</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-2.043745553237386e-05</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-5.420488014351577e-05</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-3.144180300296284e-05</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-2.573136589489877e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1692,46 +4524,190 @@
         <v>2.40564695559442e-05</v>
       </c>
       <c r="G20" t="n">
+        <v>0.0002058725076494738</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0002382016682531685</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0002585818874649704</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0001879975607153028</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0003396446409169585</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.275748738611583e-05</v>
+      </c>
+      <c r="M20" t="n">
         <v>2.613702963571995e-05</v>
       </c>
-      <c r="H20" t="n">
+      <c r="N20" t="n">
         <v>-1.525895640952513e-05</v>
       </c>
-      <c r="I20" t="n">
+      <c r="O20" t="n">
+        <v>9.171820420306176e-05</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-8.977854304248467e-05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-2.234166913694935e-07</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9.635054084355943e-06</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.40477708959952e-05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.6628573575872e-05</v>
+      </c>
+      <c r="U20" t="n">
         <v>-0.0002728893887251616</v>
       </c>
-      <c r="J20" t="n">
+      <c r="V20" t="n">
         <v>-1.858687755884603e-05</v>
       </c>
-      <c r="K20" t="n">
+      <c r="W20" t="n">
+        <v>-0.0001011649510473944</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.0001216528544318862</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.869269908638671e-05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.0001683376758592203</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.0003022623131982982</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-1.553093534312211e-05</v>
+      </c>
+      <c r="AC20" t="n">
         <v>0.0001548152358736843</v>
       </c>
-      <c r="L20" t="n">
+      <c r="AD20" t="n">
         <v>6.371296876750421e-07</v>
       </c>
-      <c r="M20" t="n">
+      <c r="AE20" t="n">
+        <v>0.0001540678786113858</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0001840663753682747</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.0002579052525106817</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>8.314249862451106e-05</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.000151118278154172</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.28732676027721e-07</v>
+      </c>
+      <c r="AK20" t="n">
         <v>0.0006228942656889558</v>
       </c>
-      <c r="N20" t="n">
+      <c r="AL20" t="n">
         <v>4.552049722406082e-05</v>
       </c>
-      <c r="O20" t="n">
+      <c r="AM20" t="n">
+        <v>0.0003743427514564246</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.0004188977472949773</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.0003822864091489464</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.0001757938152877614</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.0006415427778847516</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.37624184996821e-05</v>
+      </c>
+      <c r="AS20" t="n">
         <v>-0.0006201280630193651</v>
       </c>
-      <c r="P20" t="n">
+      <c r="AT20" t="n">
         <v>-2.211384889960755e-05</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="AU20" t="n">
+        <v>-0.0002902039268519729</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-0.000292376906145364</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-0.0003786732559092343</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-0.0001583549455972388</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-0.0006359686958603561</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-1.819844692363404e-05</v>
+      </c>
+      <c r="BA20" t="n">
         <v>-5.379577487474307e-05</v>
       </c>
-      <c r="R20" t="n">
+      <c r="BB20" t="n">
         <v>-3.025370460818522e-05</v>
       </c>
-      <c r="S20" t="n">
+      <c r="BC20" t="n">
+        <v>5.751051503466442e-05</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-0.0001521151571068913</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-4.926990368403494e-05</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-5.089618571219034e-05</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>-7.824887870810926e-05</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>-3.022695636900607e-05</v>
+      </c>
+      <c r="BI20" t="n">
         <v>-2.333331758563872e-05</v>
       </c>
-      <c r="T20" t="n">
+      <c r="BJ20" t="n">
         <v>-2.584195499366615e-05</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.0002293615252710879</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-0.0002585576148703694</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>-1.794269883248489e-05</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-5.689248064300045e-05</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>-3.159229891025461e-05</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>-2.589009091025218e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1756,46 +4732,190 @@
         <v>2.376894553890452e-05</v>
       </c>
       <c r="G21" t="n">
+        <v>0.00020130883785896</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0002340761420782655</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0002537596737965941</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0001838473981479183</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0003291722969152033</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.249181670777034e-05</v>
+      </c>
+      <c r="M21" t="n">
         <v>2.764699274848681e-05</v>
       </c>
-      <c r="H21" t="n">
+      <c r="N21" t="n">
         <v>-1.514063569629798e-05</v>
       </c>
-      <c r="I21" t="n">
+      <c r="O21" t="n">
+        <v>8.967551548266783e-05</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-8.72979435371235e-05</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.388172101243981e-07</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.004840305540711e-05</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.60329904651735e-05</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.64605735335499e-05</v>
+      </c>
+      <c r="U21" t="n">
         <v>-0.0002663806371856481</v>
       </c>
-      <c r="J21" t="n">
+      <c r="V21" t="n">
         <v>-1.831250665418338e-05</v>
       </c>
-      <c r="K21" t="n">
+      <c r="W21" t="n">
+        <v>-9.871750080492347e-05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.0001188071255455725</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.830329529184382e-05</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.0001640144037082791</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.0002952815848402679</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-1.532192618469708e-05</v>
+      </c>
+      <c r="AC21" t="n">
         <v>0.0001446747774025425</v>
       </c>
-      <c r="L21" t="n">
+      <c r="AD21" t="n">
         <v>6.132262910796271e-07</v>
       </c>
-      <c r="M21" t="n">
+      <c r="AE21" t="n">
+        <v>0.0001507925917394459</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.00018181191990152</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.0002530983183532953</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>8.24510061647743e-05</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.0001409425458405167</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>4.121545487123512e-07</v>
+      </c>
+      <c r="AK21" t="n">
         <v>0.0006103639025241137</v>
       </c>
-      <c r="N21" t="n">
+      <c r="AL21" t="n">
         <v>4.409246321301907e-05</v>
       </c>
-      <c r="O21" t="n">
+      <c r="AM21" t="n">
+        <v>0.0003666451084427536</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.0004130033776164055</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.0003799240512307733</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.0001668873446760699</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.0006292793550528586</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.239700501784682e-05</v>
+      </c>
+      <c r="AS21" t="n">
         <v>-0.0006071937386877835</v>
       </c>
-      <c r="P21" t="n">
+      <c r="AT21" t="n">
         <v>-2.131219844159205e-05</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="AU21" t="n">
+        <v>-0.0002833495964296162</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-0.0002855060156434774</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-0.0003761950065381825</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-0.0001471056311856955</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.0006230132421478629</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-1.75502646015957e-05</v>
+      </c>
+      <c r="BA21" t="n">
         <v>-5.778911145171151e-05</v>
       </c>
-      <c r="R21" t="n">
+      <c r="BB21" t="n">
         <v>-2.915320692409296e-05</v>
       </c>
-      <c r="S21" t="n">
+      <c r="BC21" t="n">
+        <v>6.028306597727351e-05</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-0.0001584352139616385</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-5.09392048115842e-05</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-5.27221018273849e-05</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-8.301353955175728e-05</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-2.912796844611876e-05</v>
+      </c>
+      <c r="BI21" t="n">
         <v>-2.281049455632456e-05</v>
       </c>
-      <c r="T21" t="n">
+      <c r="BJ21" t="n">
         <v>-2.529873563617002e-05</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.0002247389347758144</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>-0.0002528960176277906</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>-1.499389600212453e-05</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>-5.85807028983254e-05</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>-3.091526014031842e-05</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-2.531907557568047e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1820,46 +4940,190 @@
         <v>2.34937688219361e-05</v>
       </c>
       <c r="G22" t="n">
+        <v>0.0001959507062565535</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0002287675888510421</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.000247715157456696</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0001788619119906798</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0003159795014653355</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.226258584414609e-05</v>
+      </c>
+      <c r="M22" t="n">
         <v>2.818951543304138e-05</v>
       </c>
-      <c r="H22" t="n">
+      <c r="N22" t="n">
         <v>-1.50449741340708e-05</v>
       </c>
-      <c r="I22" t="n">
+      <c r="O22" t="n">
+        <v>8.694171265233308e-05</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-8.453401824226603e-05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.939316901683924e-07</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.005047306534834e-05</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.691277743200772e-05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-1.632635394344106e-05</v>
+      </c>
+      <c r="U22" t="n">
         <v>-0.0002571249206084758</v>
       </c>
-      <c r="J22" t="n">
+      <c r="V22" t="n">
         <v>-1.803446320991497e-05</v>
       </c>
-      <c r="K22" t="n">
+      <c r="W22" t="n">
+        <v>-9.529999806545675e-05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.0001148098090197891</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.810911271604709e-05</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-0.0001584651472512633</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.0002852886391337961</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-1.512971812189789e-05</v>
+      </c>
+      <c r="AC22" t="n">
         <v>0.0001344949996564537</v>
       </c>
-      <c r="L22" t="n">
+      <c r="AD22" t="n">
         <v>6.033683348505292e-07</v>
       </c>
-      <c r="M22" t="n">
+      <c r="AE22" t="n">
+        <v>0.0001474982418585569</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.0001789058878784999</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.0002470510662533343</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>8.23369191493839e-05</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.0001307321217609569</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>4.056622913140018e-07</v>
+      </c>
+      <c r="AK22" t="n">
         <v>0.0005920177791267633</v>
       </c>
-      <c r="N22" t="n">
+      <c r="AL22" t="n">
         <v>4.246186290401965e-05</v>
       </c>
-      <c r="O22" t="n">
+      <c r="AM22" t="n">
+        <v>0.0003554995346348733</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.0004030645359307528</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.0003735151840373874</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.0001556561619509012</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.0006110688555054367</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.089683716301806e-05</v>
+      </c>
+      <c r="AS22" t="n">
         <v>-0.0005886147846467793</v>
       </c>
-      <c r="P22" t="n">
+      <c r="AT22" t="n">
         <v>-2.002491964958608e-05</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="AU22" t="n">
+        <v>-0.0002734438749030232</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-0.0002755811146926135</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>-0.000369716202840209</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>-0.0001338685251539573</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-0.0006043382454663515</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>-1.648492252570577e-05</v>
+      </c>
+      <c r="BA22" t="n">
         <v>-5.942148345638998e-05</v>
       </c>
-      <c r="R22" t="n">
+      <c r="BB22" t="n">
         <v>-2.830359699146356e-05</v>
       </c>
-      <c r="S22" t="n">
+      <c r="BC22" t="n">
+        <v>6.30970171187073e-05</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>-0.0001626682205824181</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>-5.154567406862043e-05</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>-5.3456755267689e-05</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>-8.534044900443405e-05</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>-2.828025390044786e-05</v>
+      </c>
+      <c r="BI22" t="n">
         <v>-2.206278986705001e-05</v>
       </c>
-      <c r="T22" t="n">
+      <c r="BJ22" t="n">
         <v>-2.451364707667381e-05</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0.0002182364114560187</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>-0.0002450614701956511</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>-1.290578893531347e-05</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>-5.874038106412627e-05</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>-2.995675640704576e-05</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>-2.451583168294746e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1884,46 +5148,190 @@
         <v>2.337402111152187e-05</v>
       </c>
       <c r="G23" t="n">
+        <v>0.0001942721428349614</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0002269039396196604</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0002461481199134141</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0001769276568666101</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0003130828263238072</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.216023858636618e-05</v>
+      </c>
+      <c r="M23" t="n">
         <v>2.806355223583523e-05</v>
       </c>
-      <c r="H23" t="n">
+      <c r="N23" t="n">
         <v>-1.491382408858044e-05</v>
       </c>
-      <c r="I23" t="n">
+      <c r="O23" t="n">
+        <v>8.565759344492108e-05</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-8.266085205832496e-05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.390394097863464e-07</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.033287662721705e-05</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.701500099850819e-05</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.622871786821634e-05</v>
+      </c>
+      <c r="U23" t="n">
         <v>-0.0002572503290139139</v>
       </c>
-      <c r="J23" t="n">
+      <c r="V23" t="n">
         <v>-1.798696757759899e-05</v>
       </c>
-      <c r="K23" t="n">
+      <c r="W23" t="n">
+        <v>-9.535849676467478e-05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.0001149130330304615</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.644372423470486e-05</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.0001570914027979597</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.000285495538264513</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-1.508400873717619e-05</v>
+      </c>
+      <c r="AC23" t="n">
         <v>0.0001269082276849076</v>
       </c>
-      <c r="L23" t="n">
+      <c r="AD23" t="n">
         <v>6.258305234041472e-07</v>
       </c>
-      <c r="M23" t="n">
+      <c r="AE23" t="n">
+        <v>0.0001459835621062666</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.0001773346593836322</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.0002455964568071067</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>8.073983917711303e-05</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.0001230570342158899</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>4.214118973777659e-07</v>
+      </c>
+      <c r="AK23" t="n">
         <v>0.0005917401285842061</v>
       </c>
-      <c r="N23" t="n">
+      <c r="AL23" t="n">
         <v>4.306058690417558e-05</v>
       </c>
-      <c r="O23" t="n">
+      <c r="AM23" t="n">
+        <v>0.000356302538421005</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.0004047455440741032</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.0003766536538023502</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.000153124361531809</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.0006110905087552965</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.150624590693042e-05</v>
+      </c>
+      <c r="AS23" t="n">
         <v>-0.0005884658312425017</v>
       </c>
-      <c r="P23" t="n">
+      <c r="AT23" t="n">
         <v>-2.008027149713598e-05</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="AU23" t="n">
+        <v>-0.0002736825554165989</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>-0.0002758022164925933</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>-0.0003728779847733676</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>-0.0001313018146902323</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>-0.0006044832989573479</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>-1.651427373872139e-05</v>
+      </c>
+      <c r="BA23" t="n">
         <v>-5.806978879263625e-05</v>
       </c>
-      <c r="R23" t="n">
+      <c r="BB23" t="n">
         <v>-2.905354813265149e-05</v>
       </c>
-      <c r="S23" t="n">
+      <c r="BC23" t="n">
+        <v>6.617247709073126e-05</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>-0.0001655631058383733</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>-5.139861968928017e-05</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>-5.342397707863711e-05</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>-8.442321268375963e-05</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>-2.902890628320165e-05</v>
+      </c>
+      <c r="BI23" t="n">
         <v>-2.218643021478783e-05</v>
       </c>
-      <c r="T23" t="n">
+      <c r="BJ23" t="n">
         <v>-2.463510099914856e-05</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0.0002183358883485198</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>-0.0002456439542584121</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>-1.371717917209025e-05</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>-5.790322757093236e-05</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>-3.007102895935532e-05</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>-2.464487624820322e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1948,46 +5356,190 @@
         <v>2.337189835088793e-05</v>
       </c>
       <c r="G24" t="n">
+        <v>0.0001959447981789708</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0002282761270180345</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0002487170568201691</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0001777130091795698</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0003198398917447776</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2.214209962403402e-05</v>
+      </c>
+      <c r="M24" t="n">
         <v>2.740033050940838e-05</v>
       </c>
-      <c r="H24" t="n">
+      <c r="N24" t="n">
         <v>-1.476824763813056e-05</v>
       </c>
-      <c r="I24" t="n">
+      <c r="O24" t="n">
+        <v>8.575902757002041e-05</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-8.191660890588537e-05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8.421847041972796e-07</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.077743399946485e-05</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.649203790700994e-05</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-1.615568180568516e-05</v>
+      </c>
+      <c r="U24" t="n">
         <v>-0.0002659110177773982</v>
       </c>
-      <c r="J24" t="n">
+      <c r="V24" t="n">
         <v>-1.810272442526184e-05</v>
       </c>
-      <c r="K24" t="n">
+      <c r="W24" t="n">
+        <v>-9.852176299318671e-05</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.0001186257577501237</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.375687224935973e-05</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.0001594327331986278</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.0002949991030618548</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-1.513500865257811e-05</v>
+      </c>
+      <c r="AC24" t="n">
         <v>0.0001220495978486724</v>
       </c>
-      <c r="L24" t="n">
+      <c r="AD24" t="n">
         <v>6.601825930374616e-07</v>
       </c>
-      <c r="M24" t="n">
+      <c r="AE24" t="n">
+        <v>0.0001460589410271496</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.0001769960217643529</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.0002483348653186113</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>7.776225538691506e-05</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.0001180737381218933</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>4.449771040526684e-07</v>
+      </c>
+      <c r="AK24" t="n">
         <v>0.0006083885091356933</v>
       </c>
-      <c r="N24" t="n">
+      <c r="AL24" t="n">
         <v>4.518807691056281e-05</v>
       </c>
-      <c r="O24" t="n">
+      <c r="AM24" t="n">
+        <v>0.000368076580343768</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.0004169883613940328</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.0003888255159836262</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.0001584674464538693</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.0006281264941208065</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.353325857664458e-05</v>
+      </c>
+      <c r="AS24" t="n">
         <v>-0.0006054791738279164</v>
       </c>
-      <c r="P24" t="n">
+      <c r="AT24" t="n">
         <v>-2.127338302670978e-05</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="AU24" t="n">
+        <v>-0.0002832341415341944</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-0.0002853400656022131</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>-0.0003851614892482758</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>-0.0001382428308716044</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>-0.0006220561335794628</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>-1.74845481524244e-05</v>
+      </c>
+      <c r="BA24" t="n">
         <v>-5.480234540300444e-05</v>
       </c>
-      <c r="R24" t="n">
+      <c r="BB24" t="n">
         <v>-3.066462522838265e-05</v>
       </c>
-      <c r="S24" t="n">
+      <c r="BC24" t="n">
+        <v>6.967495573917404e-05</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>-0.0001676143001532182</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>-5.064605284132995e-05</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>-5.27764786966145e-05</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>-8.139167766785249e-05</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>-3.063686381210573e-05</v>
+      </c>
+      <c r="BI24" t="n">
         <v>-2.298281106050126e-05</v>
       </c>
-      <c r="T24" t="n">
+      <c r="BJ24" t="n">
         <v>-2.547717303968966e-05</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0.0002245087962364778</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>-0.0002537041436880827</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>-1.645900192670524e-05</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>-5.670533209922723e-05</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>-3.105465657426976e-05</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>-2.551112811488565e-05</v>
       </c>
     </row>
     <row r="25">
@@ -2012,46 +5564,190 @@
         <v>2.341008621442597e-05</v>
       </c>
       <c r="G25" t="n">
+        <v>0.0001975360210053623</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0002296491438755766</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0002514622756280005</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0001776856806827709</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0003337460802868009</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.217729525000323e-05</v>
+      </c>
+      <c r="M25" t="n">
         <v>2.734193367359694e-05</v>
       </c>
-      <c r="H25" t="n">
+      <c r="N25" t="n">
         <v>-1.470213373977458e-05</v>
       </c>
-      <c r="I25" t="n">
+      <c r="O25" t="n">
+        <v>8.49467542138882e-05</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-8.055775833781809e-05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.310958156063862e-07</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.100771714845905e-05</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.537782686180435e-05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-1.614501343283337e-05</v>
+      </c>
+      <c r="U25" t="n">
         <v>-0.0002733878791332245</v>
       </c>
-      <c r="J25" t="n">
+      <c r="V25" t="n">
         <v>-1.820450779632665e-05</v>
       </c>
-      <c r="K25" t="n">
+      <c r="W25" t="n">
+        <v>-0.0001010866253636777</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.0001215984302689321</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.082741528080078e-05</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.0001602700649527833</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.0003028368810191751</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-1.519719717180124e-05</v>
+      </c>
+      <c r="AC25" t="n">
         <v>0.0001391129480907694</v>
       </c>
-      <c r="L25" t="n">
+      <c r="AD25" t="n">
         <v>6.894194370943296e-07</v>
       </c>
-      <c r="M25" t="n">
+      <c r="AE25" t="n">
+        <v>0.0001469218113925308</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.0001773781259544194</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.0002512282808311284</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>7.592455949634314e-05</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.0001357375731458887</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>4.649231470921222e-07</v>
+      </c>
+      <c r="AK25" t="n">
         <v>0.00062463094945997</v>
       </c>
-      <c r="N25" t="n">
+      <c r="AL25" t="n">
         <v>4.66783058072906e-05</v>
       </c>
-      <c r="O25" t="n">
+      <c r="AM25" t="n">
+        <v>0.0003775653021875769</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.0004264162853360176</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.0003973831189796329</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.0001641287672100589</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.0006423753802664578</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.498356065596454e-05</v>
+      </c>
+      <c r="AS25" t="n">
         <v>-0.0006217090995050967</v>
       </c>
-      <c r="P25" t="n">
+      <c r="AT25" t="n">
         <v>-2.191912062698975e-05</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="AU25" t="n">
+        <v>-0.0002911450283136219</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>-0.0002932089555542916</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>-0.0003937970323022455</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>-0.0001453531440347433</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>-0.0006369707989506423</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>-1.800549580366351e-05</v>
+      </c>
+      <c r="BA25" t="n">
         <v>-5.553895607590675e-05</v>
       </c>
-      <c r="R25" t="n">
+      <c r="BB25" t="n">
         <v>-3.189448398188688e-05</v>
       </c>
-      <c r="S25" t="n">
+      <c r="BC25" t="n">
+        <v>7.090305734891444e-05</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.0001675236562732607</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-4.984857150702737e-05</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-5.198559665586799e-05</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>-7.68121681176126e-05</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>-3.186508183716796e-05</v>
+      </c>
+      <c r="BI25" t="n">
         <v>-2.360234066145495e-05</v>
       </c>
-      <c r="T25" t="n">
+      <c r="BJ25" t="n">
         <v>-2.609901093819644e-05</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0.0002297017344972119</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>-0.0002603750617709011</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>-1.877093018265441e-05</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>-5.575135219260119e-05</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>-3.18470956699457e-05</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>-2.615223274915479e-05</v>
       </c>
     </row>
     <row r="26">
@@ -2076,46 +5772,190 @@
         <v>2.356942422920838e-05</v>
       </c>
       <c r="G26" t="n">
+        <v>0.0001998420630116016</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0002316841710126027</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.0002542850852478296</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0001781510072760284</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0003635605680756271</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.236470754723996e-05</v>
+      </c>
+      <c r="M26" t="n">
         <v>2.820752524712589e-05</v>
       </c>
-      <c r="H26" t="n">
+      <c r="N26" t="n">
         <v>-1.48317230923567e-05</v>
       </c>
-      <c r="I26" t="n">
+      <c r="O26" t="n">
+        <v>8.432992035523057e-05</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-8.029274613363668e-05</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.674883804980709e-07</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.057980261975899e-05</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.289705273346044e-05</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1.629641701583751e-05</v>
+      </c>
+      <c r="U26" t="n">
         <v>-0.0002750035200733691</v>
       </c>
-      <c r="J26" t="n">
+      <c r="V26" t="n">
         <v>-1.830387918744236e-05</v>
       </c>
-      <c r="K26" t="n">
+      <c r="W26" t="n">
+        <v>-0.0001013129585771821</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.0001218305187649094</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.019435876514763e-05</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.000159654940944165</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.0003035576082766056</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1.530936242488679e-05</v>
+      </c>
+      <c r="AC26" t="n">
         <v>0.000199062837054953</v>
       </c>
-      <c r="L26" t="n">
+      <c r="AD26" t="n">
         <v>7.111736408660363e-07</v>
       </c>
-      <c r="M26" t="n">
+      <c r="AE26" t="n">
+        <v>0.0001502031955169514</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.0001799665333237499</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.0002540806017350405</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>7.833356357878074e-05</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.0001973495382117108</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4.799728117177438e-07</v>
+      </c>
+      <c r="AK26" t="n">
         <v>0.0006317530060186982</v>
       </c>
-      <c r="N26" t="n">
+      <c r="AL26" t="n">
         <v>4.673010698752478e-05</v>
       </c>
-      <c r="O26" t="n">
+      <c r="AM26" t="n">
+        <v>0.0003762728301808238</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.0004216937813907862</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.0003845898900181055</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.0001760222803568467</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.0006439615390263498</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.512765008257702e-05</v>
+      </c>
+      <c r="AS26" t="n">
         <v>-0.0006282792310230434</v>
       </c>
-      <c r="P26" t="n">
+      <c r="AT26" t="n">
         <v>-2.134111491614021e-05</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="AU26" t="n">
+        <v>-0.000291854259558022</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>-0.0002939048572443426</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>-0.0003809230693150312</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>-0.0001594941131770611</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>-0.0006393577205017209</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>-1.751215859258082e-05</v>
+      </c>
+      <c r="BA26" t="n">
         <v>-6.178929470479488e-05</v>
       </c>
-      <c r="R26" t="n">
+      <c r="BB26" t="n">
         <v>-3.237969212932512e-05</v>
       </c>
-      <c r="S26" t="n">
+      <c r="BC26" t="n">
+        <v>5.741304630646482e-05</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>-0.0001524147810414433</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>-4.898786573903635e-05</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-5.056894588051364e-05</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>-6.990406836848706e-05</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>-3.235159238101915e-05</v>
+      </c>
+      <c r="BI26" t="n">
         <v>-2.364645661145914e-05</v>
       </c>
-      <c r="T26" t="n">
+      <c r="BJ26" t="n">
         <v>-2.607326314318925e-05</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0.0002304475347045809</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>-0.000261180626694113</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>-2.017889892158564e-05</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>-5.466492439154536e-05</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>-3.196184479747899e-05</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>-2.613816286611836e-05</v>
       </c>
     </row>
     <row r="27">
@@ -2140,46 +5980,190 @@
         <v>2.378618046350311e-05</v>
       </c>
       <c r="G27" t="n">
+        <v>0.0002024364366661757</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0002337457262910903</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0002552879159338772</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0001821692567318678</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0003569961700122803</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.258411404909566e-05</v>
+      </c>
+      <c r="M27" t="n">
         <v>2.575327016529627e-05</v>
       </c>
-      <c r="H27" t="n">
+      <c r="N27" t="n">
         <v>-1.507160413893871e-05</v>
       </c>
-      <c r="I27" t="n">
+      <c r="O27" t="n">
+        <v>8.747010724619031e-05</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-8.53528908919543e-05</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-6.701471875203424e-07</v>
+      </c>
+      <c r="R27" t="n">
+        <v>9.272669558413327e-06</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.09009374177549e-05</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-1.649907972023357e-05</v>
+      </c>
+      <c r="U27" t="n">
         <v>-0.0002712101850192994</v>
       </c>
-      <c r="J27" t="n">
+      <c r="V27" t="n">
         <v>-1.8388749595033e-05</v>
       </c>
-      <c r="K27" t="n">
+      <c r="W27" t="n">
+        <v>-0.0001000630290945992</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.0001203807114507072</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.516772408649558e-05</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-0.0001626559096621349</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.0002996470429934561</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-1.541435995022766e-05</v>
+      </c>
+      <c r="AC27" t="n">
         <v>0.0001939575013238937</v>
       </c>
-      <c r="L27" t="n">
+      <c r="AD27" t="n">
         <v>6.949795761101996e-07</v>
       </c>
-      <c r="M27" t="n">
+      <c r="AE27" t="n">
+        <v>0.0001526986743556336</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.0001812744594644755</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.000254836049862206</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>8.150281064445153e-05</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.0001915804023155943</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>4.691683272994851e-07</v>
+      </c>
+      <c r="AK27" t="n">
         <v>0.0006226701661944389</v>
       </c>
-      <c r="N27" t="n">
+      <c r="AL27" t="n">
         <v>4.559161607176065e-05</v>
       </c>
-      <c r="O27" t="n">
+      <c r="AM27" t="n">
+        <v>0.0003703440306708217</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.0004115024057682604</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0.0003682372043840587</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.0001825428189476952</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.0006367632886394858</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.405780418892391e-05</v>
+      </c>
+      <c r="AS27" t="n">
         <v>-0.0006198121700435877</v>
       </c>
-      <c r="P27" t="n">
+      <c r="AT27" t="n">
         <v>-2.066072011075448e-05</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="AU27" t="n">
+        <v>-0.0002877573424484581</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-0.0002899059618357569</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>-0.000364608276868239</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>-0.0001677628606557846</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>-0.0006322689587250352</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>-1.694971797405742e-05</v>
+      </c>
+      <c r="BA27" t="n">
         <v>-5.490136754815467e-05</v>
       </c>
-      <c r="R27" t="n">
+      <c r="BB27" t="n">
         <v>-3.15554098051507e-05</v>
       </c>
-      <c r="S27" t="n">
+      <c r="BC27" t="n">
+        <v>4.737398921861313e-05</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>-0.0001378768356516957</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>-4.71311723231338e-05</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>-4.829811587114818e-05</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>-6.866545299999416e-05</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>-3.153066791128367e-05</v>
+      </c>
+      <c r="BI27" t="n">
         <v>-2.316997233720031e-05</v>
       </c>
-      <c r="T27" t="n">
+      <c r="BJ27" t="n">
         <v>-2.561222754593473e-05</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0.0002282676432514563</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>-0.0002574465761426836</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>-2.093083639920224e-05</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>-5.333664739737287e-05</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>-3.144000947941095e-05</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>-2.5682951672934e-05</v>
       </c>
     </row>
     <row r="28">
@@ -2204,46 +6188,190 @@
         <v>2.391752786934376e-05</v>
       </c>
       <c r="G28" t="n">
+        <v>0.0002044203865807503</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0002354522584937513</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0002563021844252944</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0001855278096627444</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.0003451018419582397</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.268317257403396e-05</v>
+      </c>
+      <c r="M28" t="n">
         <v>2.344592940062284e-05</v>
       </c>
-      <c r="H28" t="n">
+      <c r="N28" t="n">
         <v>-1.519877150713e-05</v>
       </c>
-      <c r="I28" t="n">
+      <c r="O28" t="n">
+        <v>8.980671555036679e-05</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-8.91909294296056e-05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.310676793764287e-06</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8.363700544578023e-06</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.985081846418325e-05</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-1.658727342146449e-05</v>
+      </c>
+      <c r="U28" t="n">
         <v>-0.0002696455048862845</v>
       </c>
-      <c r="J28" t="n">
+      <c r="V28" t="n">
         <v>-1.845537371991668e-05</v>
       </c>
-      <c r="K28" t="n">
+      <c r="W28" t="n">
+        <v>-9.975370630854741e-05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.000119993019325193</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.848083957156632e-05</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-0.0001656571112107486</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.0002983708691317588</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-1.546564089949243e-05</v>
+      </c>
+      <c r="AC28" t="n">
         <v>0.0001740088046062738</v>
       </c>
-      <c r="L28" t="n">
+      <c r="AD28" t="n">
         <v>6.667961542916601e-07</v>
       </c>
-      <c r="M28" t="n">
+      <c r="AE28" t="n">
+        <v>0.0001541805686429143</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.0001818912278395146</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.0002556316612754017</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>8.311642886837944e-05</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.0001708187483018264</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>4.501364401221508e-07</v>
+      </c>
+      <c r="AK28" t="n">
         <v>0.0006172619760036469</v>
       </c>
-      <c r="N28" t="n">
+      <c r="AL28" t="n">
         <v>4.498180715017952e-05</v>
       </c>
-      <c r="O28" t="n">
+      <c r="AM28" t="n">
+        <v>0.0003690774610731751</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.0004093126335646957</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.0003675402258522809</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.0001799673773348331</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.0006338110542856157</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4.340085433796048e-05</v>
+      </c>
+      <c r="AS28" t="n">
         <v>-0.0006149238906800747</v>
       </c>
-      <c r="P28" t="n">
+      <c r="AT28" t="n">
         <v>-2.08748497243505e-05</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="AU28" t="n">
+        <v>-0.0002863669069483876</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>-0.0002885667490772903</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>-0.0003640787908807397</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>-0.0001655555242905393</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>-0.0006292893667705357</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>-1.713636083877645e-05</v>
+      </c>
+      <c r="BA28" t="n">
         <v>-4.851696940022521e-05</v>
       </c>
-      <c r="R28" t="n">
+      <c r="BB28" t="n">
         <v>-3.068847217946313e-05</v>
       </c>
-      <c r="S28" t="n">
+      <c r="BC28" t="n">
+        <v>5.009583765058778e-05</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>-0.0001371965336147696</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>-4.560232991934754e-05</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>-4.681860082200728e-05</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>-6.883726746309549e-05</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>-3.066499630222097e-05</v>
+      </c>
+      <c r="BI28" t="n">
         <v>-2.295759622938931e-05</v>
       </c>
-      <c r="T28" t="n">
+      <c r="BJ28" t="n">
         <v>-2.54130172834266e-05</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0.0002273820282425731</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>-0.0002558186242822558</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>-2.128100095433183e-05</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>-5.279813922243193e-05</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>-3.118859240203165e-05</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>-2.548797965573613e-05</v>
       </c>
     </row>
     <row r="29">
@@ -2268,46 +6396,190 @@
         <v>2.397842763457447e-05</v>
       </c>
       <c r="G29" t="n">
+        <v>0.0002057165984297171</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0002371579612372443</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0002578795538283885</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0001874139707069844</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0003418810083530843</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.270492041134275e-05</v>
+      </c>
+      <c r="M29" t="n">
         <v>2.403202051937114e-05</v>
       </c>
-      <c r="H29" t="n">
+      <c r="N29" t="n">
         <v>-1.520140722277574e-05</v>
       </c>
-      <c r="I29" t="n">
+      <c r="O29" t="n">
+        <v>9.112255065701902e-05</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-9.004178718896583e-05</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-9.781751941773109e-07</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8.817088200885337e-06</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.130381810478866e-05</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-1.658724431763403e-05</v>
+      </c>
+      <c r="U29" t="n">
         <v>-0.000272314646281302</v>
       </c>
-      <c r="J29" t="n">
+      <c r="V29" t="n">
         <v>-1.85325388883939e-05</v>
       </c>
-      <c r="K29" t="n">
+      <c r="W29" t="n">
+        <v>-0.0001008927210932598</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-0.0001213221985381097</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.871631502581295e-05</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-0.0001678812113823369</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-0.0003015065740328282</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-1.549782609799877e-05</v>
+      </c>
+      <c r="AC29" t="n">
         <v>0.0001616645458852872</v>
       </c>
-      <c r="L29" t="n">
+      <c r="AD29" t="n">
         <v>6.536064915962925e-07</v>
       </c>
-      <c r="M29" t="n">
+      <c r="AE29" t="n">
+        <v>0.0001543912512715906</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.0001828039967222139</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.0002571975928731263</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>8.283813804155216e-05</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.000158102746354416</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>4.406244897836586e-07</v>
+      </c>
+      <c r="AK29" t="n">
         <v>0.0006215933244675398</v>
       </c>
-      <c r="N29" t="n">
+      <c r="AL29" t="n">
         <v>4.551349411485717e-05</v>
       </c>
-      <c r="O29" t="n">
+      <c r="AM29" t="n">
+        <v>0.0003731577016878873</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.0004151075554545969</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0.0003759685787372291</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.0001786662469385192</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.0006395003292709589</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.381861799629405e-05</v>
+      </c>
+      <c r="AS29" t="n">
         <v>-0.0006192251457832754</v>
       </c>
-      <c r="P29" t="n">
+      <c r="AT29" t="n">
         <v>-2.174588917114306e-05</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="AU29" t="n">
+        <v>-0.0002894878853112459</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>-0.0002916703233495355</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>-0.0003724999260157347</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>-0.0001633085048524663</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>-0.0006346342270262539</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>-1.787353539839387e-05</v>
+      </c>
+      <c r="BA29" t="n">
         <v>-4.898143379250541e-05</v>
       </c>
-      <c r="R29" t="n">
+      <c r="BB29" t="n">
         <v>-3.062124233110808e-05</v>
       </c>
-      <c r="S29" t="n">
+      <c r="BC29" t="n">
+        <v>5.449408854474314e-05</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>-0.0001437526516383514</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>-4.667113898904063e-05</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>-4.810364043805748e-05</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>-7.217044912977144e-05</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>-3.059594018850476e-05</v>
+      </c>
+      <c r="BI29" t="n">
         <v>-2.322206819371786e-05</v>
       </c>
-      <c r="T29" t="n">
+      <c r="BJ29" t="n">
         <v>-2.570863398432266e-05</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0.0002290716947754845</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>-0.0002580268774181604</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>-2.044469692918938e-05</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>-5.420329034677707e-05</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>-3.14884127874393e-05</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>-2.577783197921235e-05</v>
       </c>
     </row>
     <row r="30">
@@ -2332,46 +6604,190 @@
         <v>2.384927756793331e-05</v>
       </c>
       <c r="G30" t="n">
+        <v>0.0002043966378550977</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0002366142580285668</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.0002570842043496668</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0001864487567218021</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.0003386129392310977</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.255780782434158e-05</v>
+      </c>
+      <c r="M30" t="n">
         <v>2.636346107465215e-05</v>
       </c>
-      <c r="H30" t="n">
+      <c r="N30" t="n">
         <v>-1.509590219939128e-05</v>
       </c>
-      <c r="I30" t="n">
+      <c r="O30" t="n">
+        <v>9.102043986786157e-05</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-8.863068069331348e-05</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-3.377545354510403e-08</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9.891834451991599e-06</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.432197627262212e-05</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-1.646928467380349e-05</v>
+      </c>
+      <c r="U30" t="n">
         <v>-0.0002731448330450803</v>
       </c>
-      <c r="J30" t="n">
+      <c r="V30" t="n">
         <v>-1.845246879383922e-05</v>
       </c>
-      <c r="K30" t="n">
+      <c r="W30" t="n">
+        <v>-0.0001011967979138717</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.000121700759336818</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.775391865521669e-05</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.0001674194791121408</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-0.0003025547775905579</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-1.540884841233492e-05</v>
+      </c>
+      <c r="AC30" t="n">
         <v>0.0001518206699984148</v>
       </c>
-      <c r="L30" t="n">
+      <c r="AD30" t="n">
         <v>6.388225415321358e-07</v>
       </c>
-      <c r="M30" t="n">
+      <c r="AE30" t="n">
+        <v>0.0001524876133771613</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.0001825372164603323</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.0002564704336691648</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>8.146170148393139e-05</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.0001481260696891695</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>4.298391615975561e-07</v>
+      </c>
+      <c r="AK30" t="n">
         <v>0.000623416795860976</v>
       </c>
-      <c r="N30" t="n">
+      <c r="AL30" t="n">
         <v>4.563060065265745e-05</v>
       </c>
-      <c r="O30" t="n">
+      <c r="AM30" t="n">
+        <v>0.0003747341397684067</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.0004194028442725539</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.0003827289619948715</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.0001763030304573476</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.0006420692661777139</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4.386690488900058e-05</v>
+      </c>
+      <c r="AS30" t="n">
         <v>-0.0006206419784575701</v>
       </c>
-      <c r="P30" t="n">
+      <c r="AT30" t="n">
         <v>-2.217488690803293e-05</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="AU30" t="n">
+        <v>-0.0002906248846556991</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>-0.000292789307422936</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>-0.0003791082999669015</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>-0.0001588920276844874</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>-0.0006364914588630199</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>-1.82488547579851e-05</v>
+      </c>
+      <c r="BA30" t="n">
         <v>-5.390337173594162e-05</v>
       </c>
-      <c r="R30" t="n">
+      <c r="BB30" t="n">
         <v>-3.033739267266355e-05</v>
       </c>
-      <c r="S30" t="n">
+      <c r="BC30" t="n">
+        <v>5.739574407925829e-05</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>-0.0001521934173069894</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>-4.935574179398827e-05</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>-5.098864494357258e-05</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>-7.829878450138494e-05</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>-3.031027335964609e-05</v>
+      </c>
+      <c r="BI30" t="n">
         <v>-2.337668593099806e-05</v>
       </c>
-      <c r="T30" t="n">
+      <c r="BJ30" t="n">
         <v>-2.58856889558956e-05</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0.0002294963487656787</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>-0.0002588635543361306</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>-1.795493517420255e-05</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>-5.688798046321608e-05</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>-3.163655856042169e-05</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>-2.593399221950676e-05</v>
       </c>
     </row>
     <row r="31">
@@ -2396,46 +6812,190 @@
         <v>2.356399272684939e-05</v>
       </c>
       <c r="G31" t="n">
+        <v>0.0001998692314373329</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0002325225941604003</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.0002522948198020458</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0001823344937292859</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.0003282303805463016</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.229404162790161e-05</v>
+      </c>
+      <c r="M31" t="n">
         <v>2.785740434774198e-05</v>
       </c>
-      <c r="H31" t="n">
+      <c r="N31" t="n">
         <v>-1.497976973041659e-05</v>
       </c>
-      <c r="I31" t="n">
+      <c r="O31" t="n">
+        <v>8.900043758330867e-05</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-8.619149593869224e-05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6.202066629157343e-07</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.029375016514678e-05</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.628765989560634e-05</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-1.630296355870087e-05</v>
+      </c>
+      <c r="U31" t="n">
         <v>-0.0002666301734279841</v>
       </c>
-      <c r="J31" t="n">
+      <c r="V31" t="n">
         <v>-1.817939846660011e-05</v>
       </c>
-      <c r="K31" t="n">
+      <c r="W31" t="n">
+        <v>-9.874797979136929e-05</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-0.0001188531823572703</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.739778781484347e-05</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-0.000163127260748297</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-0.000295567064313218</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-1.520089153927984e-05</v>
+      </c>
+      <c r="AC31" t="n">
         <v>0.0001417822350049391</v>
       </c>
-      <c r="L31" t="n">
+      <c r="AD31" t="n">
         <v>6.145518227640423e-07</v>
       </c>
-      <c r="M31" t="n">
+      <c r="AE31" t="n">
+        <v>0.0001492496667196974</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.0001803100312827155</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.0002516934764571488</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>8.08047188911587e-05</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.0001380525209242478</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>4.13012656963474e-07</v>
+      </c>
+      <c r="AK31" t="n">
         <v>0.0006108812522143126</v>
       </c>
-      <c r="N31" t="n">
+      <c r="AL31" t="n">
         <v>4.419490142026916e-05</v>
       </c>
-      <c r="O31" t="n">
+      <c r="AM31" t="n">
+        <v>0.0003670251171570271</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.0004134735791012645</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.0003803216386586428</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.0001674001396168023</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.0006297978688962758</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4.249318590154871e-05</v>
+      </c>
+      <c r="AS31" t="n">
         <v>-0.00060770392883569</v>
       </c>
-      <c r="P31" t="n">
+      <c r="AT31" t="n">
         <v>-2.137602132279426e-05</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="AU31" t="n">
+        <v>-0.0002837624051608145</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>-0.0002859107044059783</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>-0.000376586482161656</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>-0.0001476632169215009</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>-0.0006235308828763664</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>-1.760310988174751e-05</v>
+      </c>
+      <c r="BA31" t="n">
         <v>-5.787628469988704e-05</v>
       </c>
-      <c r="R31" t="n">
+      <c r="BB31" t="n">
         <v>-2.922556632256601e-05</v>
       </c>
-      <c r="S31" t="n">
+      <c r="BC31" t="n">
+        <v>6.015192775521427e-05</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>-0.0001584613637533039</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>-5.100849739392288e-05</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>-5.279654942569323e-05</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>-8.304344373755157e-05</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>-2.919998223660514e-05</v>
+      </c>
+      <c r="BI31" t="n">
         <v>-2.285151276737452e-05</v>
       </c>
-      <c r="T31" t="n">
+      <c r="BJ31" t="n">
         <v>-2.534010673116427e-05</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0.0002248734672321007</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>-0.0002531905483920127</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>-1.501007227489026e-05</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>-5.857393989572302e-05</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>-3.09573661070317e-05</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>-2.536064857849851e-05</v>
       </c>
     </row>
     <row r="32">
@@ -2460,46 +7020,190 @@
         <v>2.329185008420609e-05</v>
       </c>
       <c r="G32" t="n">
+        <v>0.0001945451804203913</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0002272476267535239</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.000246284733293578</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.0001773784024408087</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.000315115466946736</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.206758654210716e-05</v>
+      </c>
+      <c r="M32" t="n">
         <v>2.838632281054743e-05</v>
       </c>
-      <c r="H32" t="n">
+      <c r="N32" t="n">
         <v>-1.488685120420996e-05</v>
       </c>
-      <c r="I32" t="n">
+      <c r="O32" t="n">
+        <v>8.628880459582433e-05</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-8.346683898707852e-05</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>9.67852088251675e-07</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.028547376336064e-05</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.715087586897425e-05</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-1.617108318896499e-05</v>
+      </c>
+      <c r="U32" t="n">
         <v>-0.0002573690435383469</v>
       </c>
-      <c r="J32" t="n">
+      <c r="V32" t="n">
         <v>-1.790325950423721e-05</v>
       </c>
-      <c r="K32" t="n">
+      <c r="W32" t="n">
+        <v>-9.532945114187896e-05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-0.0001148544542957097</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.7235235645785e-05</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.0001576080685481429</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-0.0002855678321793675</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-1.501030965300743e-05</v>
+      </c>
+      <c r="AC32" t="n">
         <v>0.0001317000132985413</v>
       </c>
-      <c r="L32" t="n">
+      <c r="AD32" t="n">
         <v>6.04404476689524e-07</v>
       </c>
-      <c r="M32" t="n">
+      <c r="AE32" t="n">
+        <v>0.0001459943887311965</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.0001774351403582841</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.0002456790243741125</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>8.072796481428668e-05</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.0001279397256439552</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>4.063246876739868e-07</v>
+      </c>
+      <c r="AK32" t="n">
         <v>0.0005925301229581237</v>
       </c>
-      <c r="N32" t="n">
+      <c r="AL32" t="n">
         <v>4.255780004314147e-05</v>
       </c>
-      <c r="O32" t="n">
+      <c r="AM32" t="n">
+        <v>0.0003558681928552687</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.0004035035672131926</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.0003738760715350509</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.0001561643293825909</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.0006115802680142224</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4.09861168009229e-05</v>
+      </c>
+      <c r="AS32" t="n">
         <v>-0.000589121482335031</v>
       </c>
-      <c r="P32" t="n">
+      <c r="AT32" t="n">
         <v>-2.009065610764083e-05</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="AU32" t="n">
+        <v>-0.0002738485927693546</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>-0.0002759781200438738</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>-0.0003700722882058471</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>-0.0001344387128483504</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>-0.0006048513459973037</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>-1.653945764701348e-05</v>
+      </c>
+      <c r="BA32" t="n">
         <v>-5.94924385950435e-05</v>
       </c>
-      <c r="R32" t="n">
+      <c r="BB32" t="n">
         <v>-2.836692146956921e-05</v>
       </c>
-      <c r="S32" t="n">
+      <c r="BC32" t="n">
+        <v>6.295408820733428e-05</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>-0.0001626542361918837</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>-5.160191358299926e-05</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>-5.351697109290399e-05</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>-8.535492088412866e-05</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>-2.834325459843967e-05</v>
+      </c>
+      <c r="BI32" t="n">
         <v>-2.210177808592562e-05</v>
       </c>
-      <c r="T32" t="n">
+      <c r="BJ32" t="n">
         <v>-2.455299909343012e-05</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0.0002183710312237963</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>-0.0002453462802805007</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>-1.292511024075793e-05</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>-5.873212285223417e-05</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>-2.999701973749325e-05</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>-2.455541107337922e-05</v>
       </c>
     </row>
     <row r="33">
@@ -2524,46 +7228,190 @@
         <v>2.317603320989292e-05</v>
       </c>
       <c r="G33" t="n">
+        <v>0.0001929094869410619</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0002254297578474507</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.0002447590522933751</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.0001754923578118905</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.0003123079077340662</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.196873174398206e-05</v>
+      </c>
+      <c r="M33" t="n">
         <v>2.824868533934932e-05</v>
       </c>
-      <c r="H33" t="n">
+      <c r="N33" t="n">
         <v>-1.475886983826058e-05</v>
       </c>
-      <c r="I33" t="n">
+      <c r="O33" t="n">
+        <v>8.50261130835861e-05</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-8.16310421214439e-05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.106096419789537e-06</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.055833672580775e-05</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.723888221429661e-05</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-1.607628291822039e-05</v>
+      </c>
+      <c r="U33" t="n">
         <v>-0.0002574886602815241</v>
       </c>
-      <c r="J33" t="n">
+      <c r="V33" t="n">
         <v>-1.785809581633657e-05</v>
       </c>
-      <c r="K33" t="n">
+      <c r="W33" t="n">
+        <v>-9.538690210320055e-05</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-0.0001149562522186898</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.560014061396942e-05</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-0.0001562630495755002</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-0.0002857680665329099</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-1.496663844591239e-05</v>
+      </c>
+      <c r="AC33" t="n">
         <v>0.0001242067664861679</v>
       </c>
-      <c r="L33" t="n">
+      <c r="AD33" t="n">
         <v>6.266337209126505e-07</v>
       </c>
-      <c r="M33" t="n">
+      <c r="AE33" t="n">
+        <v>0.0001445197849534452</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.0001758977305144072</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.0002442588738631457</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>7.917035691207275e-05</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.000120358236017637</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>4.219167237806687e-07</v>
+      </c>
+      <c r="AK33" t="n">
         <v>0.0005922461277805269</v>
       </c>
-      <c r="N33" t="n">
+      <c r="AL33" t="n">
         <v>4.315086698625237e-05</v>
       </c>
-      <c r="O33" t="n">
+      <c r="AM33" t="n">
+        <v>0.0003566608938854188</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.0004051593423355371</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.0003769839240703732</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.000153631903231144</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.0006115945288911462</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4.158958472544327e-05</v>
+      </c>
+      <c r="AS33" t="n">
         <v>-0.000588967464864254</v>
       </c>
-      <c r="P33" t="n">
+      <c r="AT33" t="n">
         <v>-2.014704477915075e-05</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="AU33" t="n">
+        <v>-0.000274078396614641</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>-0.0002761907526291907</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>-0.0003732045006472617</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>-0.000131877459352836</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>-0.0006049905205145478</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>-1.656975473451894e-05</v>
+      </c>
+      <c r="BA33" t="n">
         <v>-5.812813105876558e-05</v>
       </c>
-      <c r="R33" t="n">
+      <c r="BB33" t="n">
         <v>-2.910939292632975e-05</v>
       </c>
-      <c r="S33" t="n">
+      <c r="BC33" t="n">
+        <v>6.602150097023696e-05</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>-0.0001655185624258593</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>-5.144455644767731e-05</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>-5.347295154933818e-05</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>-8.442613034276292e-05</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>-2.908444912463892e-05</v>
+      </c>
+      <c r="BI33" t="n">
         <v>-2.222354123659898e-05</v>
       </c>
-      <c r="T33" t="n">
+      <c r="BJ33" t="n">
         <v>-2.467259582772385e-05</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0.0002184701297665015</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>-0.0002459194511175156</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>-1.373864961351501e-05</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>-5.789420902146958e-05</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>-3.010958607774228e-05</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>-2.468261664034799e-05</v>
       </c>
     </row>
   </sheetData>
